--- a/workshop_report/data/plans_extra_variant.xlsx
+++ b/workshop_report/data/plans_extra_variant.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D577"/>
+  <dimension ref="A1:F577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>plan_qty</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>plan_energy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>plan_time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +467,12 @@
       <c r="D2" t="n">
         <v>108</v>
       </c>
+      <c r="E2" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +493,12 @@
       <c r="D3" t="n">
         <v>121</v>
       </c>
+      <c r="E3" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +519,12 @@
       <c r="D4" t="n">
         <v>98</v>
       </c>
+      <c r="E4" t="n">
+        <v>153.87</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32.57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +545,12 @@
       <c r="D5" t="n">
         <v>84</v>
       </c>
+      <c r="E5" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>58.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -537,6 +571,12 @@
       <c r="D6" t="n">
         <v>112</v>
       </c>
+      <c r="E6" t="n">
+        <v>151.96</v>
+      </c>
+      <c r="F6" t="n">
+        <v>88.68000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +597,12 @@
       <c r="D7" t="n">
         <v>77</v>
       </c>
+      <c r="E7" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>59.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -577,6 +623,12 @@
       <c r="D8" t="n">
         <v>130</v>
       </c>
+      <c r="E8" t="n">
+        <v>122.02</v>
+      </c>
+      <c r="F8" t="n">
+        <v>58.23</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -597,6 +649,12 @@
       <c r="D9" t="n">
         <v>90</v>
       </c>
+      <c r="E9" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>58.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -617,6 +675,12 @@
       <c r="D10" t="n">
         <v>108</v>
       </c>
+      <c r="E10" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -637,6 +701,12 @@
       <c r="D11" t="n">
         <v>127</v>
       </c>
+      <c r="E11" t="n">
+        <v>157.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -657,6 +727,12 @@
       <c r="D12" t="n">
         <v>88</v>
       </c>
+      <c r="E12" t="n">
+        <v>120.71</v>
+      </c>
+      <c r="F12" t="n">
+        <v>72.36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -677,6 +753,12 @@
       <c r="D13" t="n">
         <v>92</v>
       </c>
+      <c r="E13" t="n">
+        <v>122.19</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -697,6 +779,12 @@
       <c r="D14" t="n">
         <v>80</v>
       </c>
+      <c r="E14" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -717,6 +805,12 @@
       <c r="D15" t="n">
         <v>80</v>
       </c>
+      <c r="E15" t="n">
+        <v>125.11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24.47</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -737,6 +831,12 @@
       <c r="D16" t="n">
         <v>93</v>
       </c>
+      <c r="E16" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>15.8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -757,6 +857,12 @@
       <c r="D17" t="n">
         <v>122</v>
       </c>
+      <c r="E17" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -777,6 +883,12 @@
       <c r="D18" t="n">
         <v>105</v>
       </c>
+      <c r="E18" t="n">
+        <v>135.38</v>
+      </c>
+      <c r="F18" t="n">
+        <v>61.66</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -797,6 +909,12 @@
       <c r="D19" t="n">
         <v>109</v>
       </c>
+      <c r="E19" t="n">
+        <v>123.79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -817,6 +935,12 @@
       <c r="D20" t="n">
         <v>93</v>
       </c>
+      <c r="E20" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="F20" t="n">
+        <v>76.20999999999999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -837,6 +961,12 @@
       <c r="D21" t="n">
         <v>72</v>
       </c>
+      <c r="E21" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54.94</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -857,6 +987,12 @@
       <c r="D22" t="n">
         <v>91</v>
       </c>
+      <c r="E22" t="n">
+        <v>127.97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36.98</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -877,6 +1013,12 @@
       <c r="D23" t="n">
         <v>122</v>
       </c>
+      <c r="E23" t="n">
+        <v>99</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.04</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -897,6 +1039,12 @@
       <c r="D24" t="n">
         <v>71</v>
       </c>
+      <c r="E24" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30.87</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -917,6 +1065,12 @@
       <c r="D25" t="n">
         <v>93</v>
       </c>
+      <c r="E25" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>55.12</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -937,6 +1091,12 @@
       <c r="D26" t="n">
         <v>113</v>
       </c>
+      <c r="E26" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="F26" t="n">
+        <v>39.67</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -957,6 +1117,12 @@
       <c r="D27" t="n">
         <v>99</v>
       </c>
+      <c r="E27" t="n">
+        <v>146.95</v>
+      </c>
+      <c r="F27" t="n">
+        <v>61.19</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,6 +1143,12 @@
       <c r="D28" t="n">
         <v>107</v>
       </c>
+      <c r="E28" t="n">
+        <v>145.83</v>
+      </c>
+      <c r="F28" t="n">
+        <v>48.91</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -997,6 +1169,12 @@
       <c r="D29" t="n">
         <v>71</v>
       </c>
+      <c r="E29" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40.05</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1017,6 +1195,12 @@
       <c r="D30" t="n">
         <v>129</v>
       </c>
+      <c r="E30" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>61.55</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1037,6 +1221,12 @@
       <c r="D31" t="n">
         <v>90</v>
       </c>
+      <c r="E31" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33.38</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1057,6 +1247,12 @@
       <c r="D32" t="n">
         <v>102</v>
       </c>
+      <c r="E32" t="n">
+        <v>120.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>87.86</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1077,6 +1273,12 @@
       <c r="D33" t="n">
         <v>81</v>
       </c>
+      <c r="E33" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="F33" t="n">
+        <v>58.54</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1097,6 +1299,12 @@
       <c r="D34" t="n">
         <v>127</v>
       </c>
+      <c r="E34" t="n">
+        <v>145.68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1117,6 +1325,12 @@
       <c r="D35" t="n">
         <v>91</v>
       </c>
+      <c r="E35" t="n">
+        <v>101.81</v>
+      </c>
+      <c r="F35" t="n">
+        <v>72.92</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1137,6 +1351,12 @@
       <c r="D36" t="n">
         <v>130</v>
       </c>
+      <c r="E36" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="F36" t="n">
+        <v>67.02</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1157,6 +1377,12 @@
       <c r="D37" t="n">
         <v>113</v>
       </c>
+      <c r="E37" t="n">
+        <v>147.81</v>
+      </c>
+      <c r="F37" t="n">
+        <v>92.76000000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1177,6 +1403,12 @@
       <c r="D38" t="n">
         <v>94</v>
       </c>
+      <c r="E38" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="F38" t="n">
+        <v>70.48999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1197,6 +1429,12 @@
       <c r="D39" t="n">
         <v>118</v>
       </c>
+      <c r="E39" t="n">
+        <v>129.76</v>
+      </c>
+      <c r="F39" t="n">
+        <v>55.33</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1217,6 +1455,12 @@
       <c r="D40" t="n">
         <v>96</v>
       </c>
+      <c r="E40" t="n">
+        <v>124.87</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16.02</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1237,6 +1481,12 @@
       <c r="D41" t="n">
         <v>128</v>
       </c>
+      <c r="E41" t="n">
+        <v>153.92</v>
+      </c>
+      <c r="F41" t="n">
+        <v>44.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1257,6 +1507,12 @@
       <c r="D42" t="n">
         <v>111</v>
       </c>
+      <c r="E42" t="n">
+        <v>164.86</v>
+      </c>
+      <c r="F42" t="n">
+        <v>61.74</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1277,6 +1533,12 @@
       <c r="D43" t="n">
         <v>97</v>
       </c>
+      <c r="E43" t="n">
+        <v>128.71</v>
+      </c>
+      <c r="F43" t="n">
+        <v>60.64</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1297,6 +1559,12 @@
       <c r="D44" t="n">
         <v>129</v>
       </c>
+      <c r="E44" t="n">
+        <v>120.01</v>
+      </c>
+      <c r="F44" t="n">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1317,6 +1585,12 @@
       <c r="D45" t="n">
         <v>85</v>
       </c>
+      <c r="E45" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.63</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1337,6 +1611,12 @@
       <c r="D46" t="n">
         <v>84</v>
       </c>
+      <c r="E46" t="n">
+        <v>110.37</v>
+      </c>
+      <c r="F46" t="n">
+        <v>65.2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1357,6 +1637,12 @@
       <c r="D47" t="n">
         <v>116</v>
       </c>
+      <c r="E47" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>103.04</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1377,6 +1663,12 @@
       <c r="D48" t="n">
         <v>120</v>
       </c>
+      <c r="E48" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="F48" t="n">
+        <v>65.31</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1397,6 +1689,12 @@
       <c r="D49" t="n">
         <v>113</v>
       </c>
+      <c r="E49" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>31.5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1417,6 +1715,12 @@
       <c r="D50" t="n">
         <v>124</v>
       </c>
+      <c r="E50" t="n">
+        <v>156.29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>43.92</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1437,6 +1741,12 @@
       <c r="D51" t="n">
         <v>121</v>
       </c>
+      <c r="E51" t="n">
+        <v>134.37</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19.82</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1457,6 +1767,12 @@
       <c r="D52" t="n">
         <v>126</v>
       </c>
+      <c r="E52" t="n">
+        <v>165.64</v>
+      </c>
+      <c r="F52" t="n">
+        <v>105.3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1477,6 +1793,12 @@
       <c r="D53" t="n">
         <v>72</v>
       </c>
+      <c r="E53" t="n">
+        <v>84</v>
+      </c>
+      <c r="F53" t="n">
+        <v>17.16</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1497,6 +1819,12 @@
       <c r="D54" t="n">
         <v>106</v>
       </c>
+      <c r="E54" t="n">
+        <v>131.07</v>
+      </c>
+      <c r="F54" t="n">
+        <v>61.73</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1517,6 +1845,12 @@
       <c r="D55" t="n">
         <v>120</v>
       </c>
+      <c r="E55" t="n">
+        <v>186.38</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.66</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1537,6 +1871,12 @@
       <c r="D56" t="n">
         <v>76</v>
       </c>
+      <c r="E56" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.99</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1557,6 +1897,12 @@
       <c r="D57" t="n">
         <v>90</v>
       </c>
+      <c r="E57" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="F57" t="n">
+        <v>57.47</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1577,6 +1923,12 @@
       <c r="D58" t="n">
         <v>78</v>
       </c>
+      <c r="E58" t="n">
+        <v>118.89</v>
+      </c>
+      <c r="F58" t="n">
+        <v>60.24</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1597,6 +1949,12 @@
       <c r="D59" t="n">
         <v>108</v>
       </c>
+      <c r="E59" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="F59" t="n">
+        <v>32.92</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1617,6 +1975,12 @@
       <c r="D60" t="n">
         <v>87</v>
       </c>
+      <c r="E60" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>13.77</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1637,6 +2001,12 @@
       <c r="D61" t="n">
         <v>73</v>
       </c>
+      <c r="E61" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="F61" t="n">
+        <v>18.44</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1657,6 +2027,12 @@
       <c r="D62" t="n">
         <v>94</v>
       </c>
+      <c r="E62" t="n">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>77.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1677,6 +2053,12 @@
       <c r="D63" t="n">
         <v>129</v>
       </c>
+      <c r="E63" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="F63" t="n">
+        <v>103.9</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1697,6 +2079,12 @@
       <c r="D64" t="n">
         <v>83</v>
       </c>
+      <c r="E64" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="F64" t="n">
+        <v>49.64</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1717,6 +2105,12 @@
       <c r="D65" t="n">
         <v>119</v>
       </c>
+      <c r="E65" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="F65" t="n">
+        <v>71.45</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1737,6 +2131,12 @@
       <c r="D66" t="n">
         <v>127</v>
       </c>
+      <c r="E66" t="n">
+        <v>134.01</v>
+      </c>
+      <c r="F66" t="n">
+        <v>82.39</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1757,6 +2157,12 @@
       <c r="D67" t="n">
         <v>78</v>
       </c>
+      <c r="E67" t="n">
+        <v>115.12</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.96</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1777,6 +2183,12 @@
       <c r="D68" t="n">
         <v>95</v>
       </c>
+      <c r="E68" t="n">
+        <v>77.77</v>
+      </c>
+      <c r="F68" t="n">
+        <v>79.40000000000001</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1797,6 +2209,12 @@
       <c r="D69" t="n">
         <v>122</v>
       </c>
+      <c r="E69" t="n">
+        <v>177.09</v>
+      </c>
+      <c r="F69" t="n">
+        <v>56.62</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1817,6 +2235,12 @@
       <c r="D70" t="n">
         <v>71</v>
       </c>
+      <c r="E70" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="F70" t="n">
+        <v>31.05</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1837,6 +2261,12 @@
       <c r="D71" t="n">
         <v>89</v>
       </c>
+      <c r="E71" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="F71" t="n">
+        <v>47.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1857,6 +2287,12 @@
       <c r="D72" t="n">
         <v>97</v>
       </c>
+      <c r="E72" t="n">
+        <v>131.67</v>
+      </c>
+      <c r="F72" t="n">
+        <v>17.97</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1877,6 +2313,12 @@
       <c r="D73" t="n">
         <v>116</v>
       </c>
+      <c r="E73" t="n">
+        <v>151.17</v>
+      </c>
+      <c r="F73" t="n">
+        <v>31.87</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1897,6 +2339,12 @@
       <c r="D74" t="n">
         <v>129</v>
       </c>
+      <c r="E74" t="n">
+        <v>193.76</v>
+      </c>
+      <c r="F74" t="n">
+        <v>90.75</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1917,6 +2365,12 @@
       <c r="D75" t="n">
         <v>76</v>
       </c>
+      <c r="E75" t="n">
+        <v>105.49</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.12</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1937,6 +2391,12 @@
       <c r="D76" t="n">
         <v>113</v>
       </c>
+      <c r="E76" t="n">
+        <v>163.03</v>
+      </c>
+      <c r="F76" t="n">
+        <v>68.06999999999999</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1957,6 +2417,12 @@
       <c r="D77" t="n">
         <v>130</v>
       </c>
+      <c r="E77" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="F77" t="n">
+        <v>43.42</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1977,6 +2443,12 @@
       <c r="D78" t="n">
         <v>77</v>
       </c>
+      <c r="E78" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="F78" t="n">
+        <v>34.03</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1997,6 +2469,12 @@
       <c r="D79" t="n">
         <v>116</v>
       </c>
+      <c r="E79" t="n">
+        <v>162.46</v>
+      </c>
+      <c r="F79" t="n">
+        <v>42.52</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2017,6 +2495,12 @@
       <c r="D80" t="n">
         <v>104</v>
       </c>
+      <c r="E80" t="n">
+        <v>150.33</v>
+      </c>
+      <c r="F80" t="n">
+        <v>43.34</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2037,6 +2521,12 @@
       <c r="D81" t="n">
         <v>83</v>
       </c>
+      <c r="E81" t="n">
+        <v>132.17</v>
+      </c>
+      <c r="F81" t="n">
+        <v>57.21</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2057,6 +2547,12 @@
       <c r="D82" t="n">
         <v>86</v>
       </c>
+      <c r="E82" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="F82" t="n">
+        <v>32.06</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2077,6 +2573,12 @@
       <c r="D83" t="n">
         <v>105</v>
       </c>
+      <c r="E83" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="F83" t="n">
+        <v>60.35</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2097,6 +2599,12 @@
       <c r="D84" t="n">
         <v>119</v>
       </c>
+      <c r="E84" t="n">
+        <v>169.11</v>
+      </c>
+      <c r="F84" t="n">
+        <v>60.34</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2117,6 +2625,12 @@
       <c r="D85" t="n">
         <v>109</v>
       </c>
+      <c r="E85" t="n">
+        <v>116.92</v>
+      </c>
+      <c r="F85" t="n">
+        <v>70.61</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2137,6 +2651,12 @@
       <c r="D86" t="n">
         <v>73</v>
       </c>
+      <c r="E86" t="n">
+        <v>112.76</v>
+      </c>
+      <c r="F86" t="n">
+        <v>62.24</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2157,6 +2677,12 @@
       <c r="D87" t="n">
         <v>71</v>
       </c>
+      <c r="E87" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="F87" t="n">
+        <v>49.66</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2177,6 +2703,12 @@
       <c r="D88" t="n">
         <v>75</v>
       </c>
+      <c r="E88" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="F88" t="n">
+        <v>23.34</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2197,6 +2729,12 @@
       <c r="D89" t="n">
         <v>123</v>
       </c>
+      <c r="E89" t="n">
+        <v>172.29</v>
+      </c>
+      <c r="F89" t="n">
+        <v>21.33</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2217,6 +2755,12 @@
       <c r="D90" t="n">
         <v>111</v>
       </c>
+      <c r="E90" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F90" t="n">
+        <v>38.48</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2237,6 +2781,12 @@
       <c r="D91" t="n">
         <v>73</v>
       </c>
+      <c r="E91" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="F91" t="n">
+        <v>43.53</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2257,6 +2807,12 @@
       <c r="D92" t="n">
         <v>123</v>
       </c>
+      <c r="E92" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="F92" t="n">
+        <v>23.19</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2277,6 +2833,12 @@
       <c r="D93" t="n">
         <v>98</v>
       </c>
+      <c r="E93" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="F93" t="n">
+        <v>51.18</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2297,6 +2859,12 @@
       <c r="D94" t="n">
         <v>87</v>
       </c>
+      <c r="E94" t="n">
+        <v>127.12</v>
+      </c>
+      <c r="F94" t="n">
+        <v>51.99</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2317,6 +2885,12 @@
       <c r="D95" t="n">
         <v>95</v>
       </c>
+      <c r="E95" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="F95" t="n">
+        <v>38.06</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2337,6 +2911,12 @@
       <c r="D96" t="n">
         <v>113</v>
       </c>
+      <c r="E96" t="n">
+        <v>171.36</v>
+      </c>
+      <c r="F96" t="n">
+        <v>82.28</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2357,6 +2937,12 @@
       <c r="D97" t="n">
         <v>103</v>
       </c>
+      <c r="E97" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="F97" t="n">
+        <v>23.68</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2377,6 +2963,12 @@
       <c r="D98" t="n">
         <v>79</v>
       </c>
+      <c r="E98" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="F98" t="n">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2397,6 +2989,12 @@
       <c r="D99" t="n">
         <v>105</v>
       </c>
+      <c r="E99" t="n">
+        <v>160.05</v>
+      </c>
+      <c r="F99" t="n">
+        <v>73.09</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2417,6 +3015,12 @@
       <c r="D100" t="n">
         <v>83</v>
       </c>
+      <c r="E100" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="F100" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2437,6 +3041,12 @@
       <c r="D101" t="n">
         <v>100</v>
       </c>
+      <c r="E101" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="F101" t="n">
+        <v>66.63</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2457,6 +3067,12 @@
       <c r="D102" t="n">
         <v>117</v>
       </c>
+      <c r="E102" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="F102" t="n">
+        <v>55.71</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2477,6 +3093,12 @@
       <c r="D103" t="n">
         <v>84</v>
       </c>
+      <c r="E103" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="F103" t="n">
+        <v>28.12</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2497,6 +3119,12 @@
       <c r="D104" t="n">
         <v>77</v>
       </c>
+      <c r="E104" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="F104" t="n">
+        <v>58.85</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2517,6 +3145,12 @@
       <c r="D105" t="n">
         <v>83</v>
       </c>
+      <c r="E105" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="F105" t="n">
+        <v>62.21</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2537,6 +3171,12 @@
       <c r="D106" t="n">
         <v>92</v>
       </c>
+      <c r="E106" t="n">
+        <v>106.61</v>
+      </c>
+      <c r="F106" t="n">
+        <v>61.73</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2557,6 +3197,12 @@
       <c r="D107" t="n">
         <v>129</v>
       </c>
+      <c r="E107" t="n">
+        <v>133.46</v>
+      </c>
+      <c r="F107" t="n">
+        <v>45.68</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2577,6 +3223,12 @@
       <c r="D108" t="n">
         <v>126</v>
       </c>
+      <c r="E108" t="n">
+        <v>133.93</v>
+      </c>
+      <c r="F108" t="n">
+        <v>74.68000000000001</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2597,6 +3249,12 @@
       <c r="D109" t="n">
         <v>109</v>
       </c>
+      <c r="E109" t="n">
+        <v>145.84</v>
+      </c>
+      <c r="F109" t="n">
+        <v>45.86</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2617,6 +3275,12 @@
       <c r="D110" t="n">
         <v>90</v>
       </c>
+      <c r="E110" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="F110" t="n">
+        <v>19.68</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2637,6 +3301,12 @@
       <c r="D111" t="n">
         <v>85</v>
       </c>
+      <c r="E111" t="n">
+        <v>121.83</v>
+      </c>
+      <c r="F111" t="n">
+        <v>71.23</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2657,6 +3327,12 @@
       <c r="D112" t="n">
         <v>114</v>
       </c>
+      <c r="E112" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="F112" t="n">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2677,6 +3353,12 @@
       <c r="D113" t="n">
         <v>87</v>
       </c>
+      <c r="E113" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="F113" t="n">
+        <v>75.05</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2697,6 +3379,12 @@
       <c r="D114" t="n">
         <v>116</v>
       </c>
+      <c r="E114" t="n">
+        <v>138.68</v>
+      </c>
+      <c r="F114" t="n">
+        <v>56.2</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2717,6 +3405,12 @@
       <c r="D115" t="n">
         <v>122</v>
       </c>
+      <c r="E115" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="F115" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2737,6 +3431,12 @@
       <c r="D116" t="n">
         <v>93</v>
       </c>
+      <c r="E116" t="n">
+        <v>115.28</v>
+      </c>
+      <c r="F116" t="n">
+        <v>51.75</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2757,6 +3457,12 @@
       <c r="D117" t="n">
         <v>95</v>
       </c>
+      <c r="E117" t="n">
+        <v>109.56</v>
+      </c>
+      <c r="F117" t="n">
+        <v>76.45</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2777,6 +3483,12 @@
       <c r="D118" t="n">
         <v>94</v>
       </c>
+      <c r="E118" t="n">
+        <v>141.96</v>
+      </c>
+      <c r="F118" t="n">
+        <v>65.72</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2797,6 +3509,12 @@
       <c r="D119" t="n">
         <v>129</v>
       </c>
+      <c r="E119" t="n">
+        <v>139.41</v>
+      </c>
+      <c r="F119" t="n">
+        <v>97.38</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2817,6 +3535,12 @@
       <c r="D120" t="n">
         <v>129</v>
       </c>
+      <c r="E120" t="n">
+        <v>115.28</v>
+      </c>
+      <c r="F120" t="n">
+        <v>83.09</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2837,6 +3561,12 @@
       <c r="D121" t="n">
         <v>129</v>
       </c>
+      <c r="E121" t="n">
+        <v>117.96</v>
+      </c>
+      <c r="F121" t="n">
+        <v>86.33</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2857,6 +3587,12 @@
       <c r="D122" t="n">
         <v>114</v>
       </c>
+      <c r="E122" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="F122" t="n">
+        <v>89.70999999999999</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2877,6 +3613,12 @@
       <c r="D123" t="n">
         <v>110</v>
       </c>
+      <c r="E123" t="n">
+        <v>142.4</v>
+      </c>
+      <c r="F123" t="n">
+        <v>37.1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2897,6 +3639,12 @@
       <c r="D124" t="n">
         <v>98</v>
       </c>
+      <c r="E124" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="F124" t="n">
+        <v>50.67</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2917,6 +3665,12 @@
       <c r="D125" t="n">
         <v>84</v>
       </c>
+      <c r="E125" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>26.54</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2937,6 +3691,12 @@
       <c r="D126" t="n">
         <v>114</v>
       </c>
+      <c r="E126" t="n">
+        <v>155.13</v>
+      </c>
+      <c r="F126" t="n">
+        <v>101.55</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2957,6 +3717,12 @@
       <c r="D127" t="n">
         <v>70</v>
       </c>
+      <c r="E127" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="F127" t="n">
+        <v>60.06</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2977,6 +3743,12 @@
       <c r="D128" t="n">
         <v>94</v>
       </c>
+      <c r="E128" t="n">
+        <v>137</v>
+      </c>
+      <c r="F128" t="n">
+        <v>16.88</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2997,6 +3769,12 @@
       <c r="D129" t="n">
         <v>76</v>
       </c>
+      <c r="E129" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="F129" t="n">
+        <v>51.62</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3017,6 +3795,12 @@
       <c r="D130" t="n">
         <v>78</v>
       </c>
+      <c r="E130" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="F130" t="n">
+        <v>65.83</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3037,6 +3821,12 @@
       <c r="D131" t="n">
         <v>93</v>
       </c>
+      <c r="E131" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="F131" t="n">
+        <v>26.55</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3057,6 +3847,12 @@
       <c r="D132" t="n">
         <v>70</v>
       </c>
+      <c r="E132" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="F132" t="n">
+        <v>40.32</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3077,6 +3873,12 @@
       <c r="D133" t="n">
         <v>113</v>
       </c>
+      <c r="E133" t="n">
+        <v>124.23</v>
+      </c>
+      <c r="F133" t="n">
+        <v>94.54000000000001</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3097,6 +3899,12 @@
       <c r="D134" t="n">
         <v>77</v>
       </c>
+      <c r="E134" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="F134" t="n">
+        <v>13.51</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3117,6 +3925,12 @@
       <c r="D135" t="n">
         <v>93</v>
       </c>
+      <c r="E135" t="n">
+        <v>134.87</v>
+      </c>
+      <c r="F135" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3137,6 +3951,12 @@
       <c r="D136" t="n">
         <v>80</v>
       </c>
+      <c r="E136" t="n">
+        <v>124.62</v>
+      </c>
+      <c r="F136" t="n">
+        <v>29.84</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3157,6 +3977,12 @@
       <c r="D137" t="n">
         <v>120</v>
       </c>
+      <c r="E137" t="n">
+        <v>190.66</v>
+      </c>
+      <c r="F137" t="n">
+        <v>101.2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3177,6 +4003,12 @@
       <c r="D138" t="n">
         <v>86</v>
       </c>
+      <c r="E138" t="n">
+        <v>120.63</v>
+      </c>
+      <c r="F138" t="n">
+        <v>75.53</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3197,6 +4029,12 @@
       <c r="D139" t="n">
         <v>77</v>
       </c>
+      <c r="E139" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="F139" t="n">
+        <v>66.08</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3217,6 +4055,12 @@
       <c r="D140" t="n">
         <v>104</v>
       </c>
+      <c r="E140" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="F140" t="n">
+        <v>52.59</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3237,6 +4081,12 @@
       <c r="D141" t="n">
         <v>104</v>
       </c>
+      <c r="E141" t="n">
+        <v>147.86</v>
+      </c>
+      <c r="F141" t="n">
+        <v>82.84</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3257,6 +4107,12 @@
       <c r="D142" t="n">
         <v>102</v>
       </c>
+      <c r="E142" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="F142" t="n">
+        <v>79.91</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3277,6 +4133,12 @@
       <c r="D143" t="n">
         <v>128</v>
       </c>
+      <c r="E143" t="n">
+        <v>145.84</v>
+      </c>
+      <c r="F143" t="n">
+        <v>49.83</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3297,6 +4159,12 @@
       <c r="D144" t="n">
         <v>74</v>
       </c>
+      <c r="E144" t="n">
+        <v>112.86</v>
+      </c>
+      <c r="F144" t="n">
+        <v>57.1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3317,6 +4185,12 @@
       <c r="D145" t="n">
         <v>111</v>
       </c>
+      <c r="E145" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="F145" t="n">
+        <v>19.73</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3337,6 +4211,12 @@
       <c r="D146" t="n">
         <v>108</v>
       </c>
+      <c r="E146" t="n">
+        <v>128.96</v>
+      </c>
+      <c r="F146" t="n">
+        <v>64.5</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3357,6 +4237,12 @@
       <c r="D147" t="n">
         <v>127</v>
       </c>
+      <c r="E147" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="F147" t="n">
+        <v>40.96</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3377,6 +4263,12 @@
       <c r="D148" t="n">
         <v>110</v>
       </c>
+      <c r="E148" t="n">
+        <v>129.24</v>
+      </c>
+      <c r="F148" t="n">
+        <v>26.45</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3397,6 +4289,12 @@
       <c r="D149" t="n">
         <v>97</v>
       </c>
+      <c r="E149" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="F149" t="n">
+        <v>20.15</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3417,6 +4315,12 @@
       <c r="D150" t="n">
         <v>76</v>
       </c>
+      <c r="E150" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="F150" t="n">
+        <v>51.09</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3437,6 +4341,12 @@
       <c r="D151" t="n">
         <v>78</v>
       </c>
+      <c r="E151" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="F151" t="n">
+        <v>31.58</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3457,6 +4367,12 @@
       <c r="D152" t="n">
         <v>77</v>
       </c>
+      <c r="E152" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="F152" t="n">
+        <v>53.41</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3477,6 +4393,12 @@
       <c r="D153" t="n">
         <v>81</v>
       </c>
+      <c r="E153" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="F153" t="n">
+        <v>16.12</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3497,6 +4419,12 @@
       <c r="D154" t="n">
         <v>103</v>
       </c>
+      <c r="E154" t="n">
+        <v>130.47</v>
+      </c>
+      <c r="F154" t="n">
+        <v>39.81</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3517,6 +4445,12 @@
       <c r="D155" t="n">
         <v>102</v>
       </c>
+      <c r="E155" t="n">
+        <v>160.11</v>
+      </c>
+      <c r="F155" t="n">
+        <v>56.57</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3537,6 +4471,12 @@
       <c r="D156" t="n">
         <v>117</v>
       </c>
+      <c r="E156" t="n">
+        <v>128.69</v>
+      </c>
+      <c r="F156" t="n">
+        <v>86.94</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3557,6 +4497,12 @@
       <c r="D157" t="n">
         <v>124</v>
       </c>
+      <c r="E157" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="F157" t="n">
+        <v>48.24</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3577,6 +4523,12 @@
       <c r="D158" t="n">
         <v>92</v>
       </c>
+      <c r="E158" t="n">
+        <v>137.53</v>
+      </c>
+      <c r="F158" t="n">
+        <v>56.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3597,6 +4549,12 @@
       <c r="D159" t="n">
         <v>93</v>
       </c>
+      <c r="E159" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="F159" t="n">
+        <v>75.75</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3617,6 +4575,12 @@
       <c r="D160" t="n">
         <v>106</v>
       </c>
+      <c r="E160" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="F160" t="n">
+        <v>64.86</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3637,6 +4601,12 @@
       <c r="D161" t="n">
         <v>104</v>
       </c>
+      <c r="E161" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="F161" t="n">
+        <v>33.77</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3657,6 +4627,12 @@
       <c r="D162" t="n">
         <v>113</v>
       </c>
+      <c r="E162" t="n">
+        <v>178.08</v>
+      </c>
+      <c r="F162" t="n">
+        <v>19.02</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3677,6 +4653,12 @@
       <c r="D163" t="n">
         <v>109</v>
       </c>
+      <c r="E163" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="F163" t="n">
+        <v>87.48</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3697,6 +4679,12 @@
       <c r="D164" t="n">
         <v>91</v>
       </c>
+      <c r="E164" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="F164" t="n">
+        <v>15.1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3717,6 +4705,12 @@
       <c r="D165" t="n">
         <v>96</v>
       </c>
+      <c r="E165" t="n">
+        <v>117.33</v>
+      </c>
+      <c r="F165" t="n">
+        <v>77.38</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3737,6 +4731,12 @@
       <c r="D166" t="n">
         <v>104</v>
       </c>
+      <c r="E166" t="n">
+        <v>165.81</v>
+      </c>
+      <c r="F166" t="n">
+        <v>56.86</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3757,6 +4757,12 @@
       <c r="D167" t="n">
         <v>70</v>
       </c>
+      <c r="E167" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="F167" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3777,6 +4783,12 @@
       <c r="D168" t="n">
         <v>104</v>
       </c>
+      <c r="E168" t="n">
+        <v>129.28</v>
+      </c>
+      <c r="F168" t="n">
+        <v>77.91</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3797,6 +4809,12 @@
       <c r="D169" t="n">
         <v>106</v>
       </c>
+      <c r="E169" t="n">
+        <v>167</v>
+      </c>
+      <c r="F169" t="n">
+        <v>95.23999999999999</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3817,6 +4835,12 @@
       <c r="D170" t="n">
         <v>116</v>
       </c>
+      <c r="E170" t="n">
+        <v>141.34</v>
+      </c>
+      <c r="F170" t="n">
+        <v>47.91</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3837,6 +4861,12 @@
       <c r="D171" t="n">
         <v>83</v>
       </c>
+      <c r="E171" t="n">
+        <v>108.19</v>
+      </c>
+      <c r="F171" t="n">
+        <v>60.21</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3857,6 +4887,12 @@
       <c r="D172" t="n">
         <v>72</v>
       </c>
+      <c r="E172" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="F172" t="n">
+        <v>32.5</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3877,6 +4913,12 @@
       <c r="D173" t="n">
         <v>70</v>
       </c>
+      <c r="E173" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="F173" t="n">
+        <v>35.69</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3897,6 +4939,12 @@
       <c r="D174" t="n">
         <v>74</v>
       </c>
+      <c r="E174" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="F174" t="n">
+        <v>45.93</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3917,6 +4965,12 @@
       <c r="D175" t="n">
         <v>95</v>
       </c>
+      <c r="E175" t="n">
+        <v>120.41</v>
+      </c>
+      <c r="F175" t="n">
+        <v>76.5</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3937,6 +4991,12 @@
       <c r="D176" t="n">
         <v>124</v>
       </c>
+      <c r="E176" t="n">
+        <v>188.59</v>
+      </c>
+      <c r="F176" t="n">
+        <v>110.12</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3957,6 +5017,12 @@
       <c r="D177" t="n">
         <v>83</v>
       </c>
+      <c r="E177" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="F177" t="n">
+        <v>60.28</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3977,6 +5043,12 @@
       <c r="D178" t="n">
         <v>108</v>
       </c>
+      <c r="E178" t="n">
+        <v>110.68</v>
+      </c>
+      <c r="F178" t="n">
+        <v>50.04</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3997,6 +5069,12 @@
       <c r="D179" t="n">
         <v>96</v>
       </c>
+      <c r="E179" t="n">
+        <v>149.79</v>
+      </c>
+      <c r="F179" t="n">
+        <v>44.74</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4017,6 +5095,12 @@
       <c r="D180" t="n">
         <v>78</v>
       </c>
+      <c r="E180" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="F180" t="n">
+        <v>54.85</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4037,6 +5121,12 @@
       <c r="D181" t="n">
         <v>84</v>
       </c>
+      <c r="E181" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="F181" t="n">
+        <v>27.64</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4057,6 +5147,12 @@
       <c r="D182" t="n">
         <v>84</v>
       </c>
+      <c r="E182" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="F182" t="n">
+        <v>19.56</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4077,6 +5173,12 @@
       <c r="D183" t="n">
         <v>95</v>
       </c>
+      <c r="E183" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="F183" t="n">
+        <v>39.52</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4097,6 +5199,12 @@
       <c r="D184" t="n">
         <v>111</v>
       </c>
+      <c r="E184" t="n">
+        <v>105.51</v>
+      </c>
+      <c r="F184" t="n">
+        <v>40.56</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4117,6 +5225,12 @@
       <c r="D185" t="n">
         <v>129</v>
       </c>
+      <c r="E185" t="n">
+        <v>151.05</v>
+      </c>
+      <c r="F185" t="n">
+        <v>48.02</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4137,6 +5251,12 @@
       <c r="D186" t="n">
         <v>82</v>
       </c>
+      <c r="E186" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="F186" t="n">
+        <v>26.67</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4157,6 +5277,12 @@
       <c r="D187" t="n">
         <v>120</v>
       </c>
+      <c r="E187" t="n">
+        <v>152.03</v>
+      </c>
+      <c r="F187" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4177,6 +5303,12 @@
       <c r="D188" t="n">
         <v>101</v>
       </c>
+      <c r="E188" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="F188" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4197,6 +5329,12 @@
       <c r="D189" t="n">
         <v>108</v>
       </c>
+      <c r="E189" t="n">
+        <v>170.59</v>
+      </c>
+      <c r="F189" t="n">
+        <v>96.20999999999999</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4217,6 +5355,12 @@
       <c r="D190" t="n">
         <v>118</v>
       </c>
+      <c r="E190" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="F190" t="n">
+        <v>55.56</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4237,6 +5381,12 @@
       <c r="D191" t="n">
         <v>121</v>
       </c>
+      <c r="E191" t="n">
+        <v>164.38</v>
+      </c>
+      <c r="F191" t="n">
+        <v>53.03</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4257,6 +5407,12 @@
       <c r="D192" t="n">
         <v>130</v>
       </c>
+      <c r="E192" t="n">
+        <v>159.75</v>
+      </c>
+      <c r="F192" t="n">
+        <v>85.77</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4277,6 +5433,12 @@
       <c r="D193" t="n">
         <v>101</v>
       </c>
+      <c r="E193" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="F193" t="n">
+        <v>31.68</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4297,6 +5459,12 @@
       <c r="D194" t="n">
         <v>73</v>
       </c>
+      <c r="E194" t="n">
+        <v>105.93</v>
+      </c>
+      <c r="F194" t="n">
+        <v>62.96</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4317,6 +5485,12 @@
       <c r="D195" t="n">
         <v>99</v>
       </c>
+      <c r="E195" t="n">
+        <v>133.43</v>
+      </c>
+      <c r="F195" t="n">
+        <v>73.23999999999999</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4337,6 +5511,12 @@
       <c r="D196" t="n">
         <v>106</v>
       </c>
+      <c r="E196" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="F196" t="n">
+        <v>23.01</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4357,6 +5537,12 @@
       <c r="D197" t="n">
         <v>92</v>
       </c>
+      <c r="E197" t="n">
+        <v>140.64</v>
+      </c>
+      <c r="F197" t="n">
+        <v>42.61</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4377,6 +5563,12 @@
       <c r="D198" t="n">
         <v>108</v>
       </c>
+      <c r="E198" t="n">
+        <v>157.47</v>
+      </c>
+      <c r="F198" t="n">
+        <v>87.41</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4397,6 +5589,12 @@
       <c r="D199" t="n">
         <v>114</v>
       </c>
+      <c r="E199" t="n">
+        <v>177.82</v>
+      </c>
+      <c r="F199" t="n">
+        <v>97.87</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4417,6 +5615,12 @@
       <c r="D200" t="n">
         <v>84</v>
       </c>
+      <c r="E200" t="n">
+        <v>115.97</v>
+      </c>
+      <c r="F200" t="n">
+        <v>42.05</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4437,6 +5641,12 @@
       <c r="D201" t="n">
         <v>112</v>
       </c>
+      <c r="E201" t="n">
+        <v>144.56</v>
+      </c>
+      <c r="F201" t="n">
+        <v>68.33</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4457,6 +5667,12 @@
       <c r="D202" t="n">
         <v>98</v>
       </c>
+      <c r="E202" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="F202" t="n">
+        <v>26.98</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4477,6 +5693,12 @@
       <c r="D203" t="n">
         <v>105</v>
       </c>
+      <c r="E203" t="n">
+        <v>162.35</v>
+      </c>
+      <c r="F203" t="n">
+        <v>93.8</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4497,6 +5719,12 @@
       <c r="D204" t="n">
         <v>82</v>
       </c>
+      <c r="E204" t="n">
+        <v>122.41</v>
+      </c>
+      <c r="F204" t="n">
+        <v>26.55</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4517,6 +5745,12 @@
       <c r="D205" t="n">
         <v>101</v>
       </c>
+      <c r="E205" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="F205" t="n">
+        <v>86.56</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4537,6 +5771,12 @@
       <c r="D206" t="n">
         <v>76</v>
       </c>
+      <c r="E206" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>48.43</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4557,6 +5797,12 @@
       <c r="D207" t="n">
         <v>128</v>
       </c>
+      <c r="E207" t="n">
+        <v>140.95</v>
+      </c>
+      <c r="F207" t="n">
+        <v>77.54000000000001</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4577,6 +5823,12 @@
       <c r="D208" t="n">
         <v>120</v>
       </c>
+      <c r="E208" t="n">
+        <v>173.81</v>
+      </c>
+      <c r="F208" t="n">
+        <v>64.14</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4597,6 +5849,12 @@
       <c r="D209" t="n">
         <v>91</v>
       </c>
+      <c r="E209" t="n">
+        <v>144.67</v>
+      </c>
+      <c r="F209" t="n">
+        <v>29.39</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4617,6 +5875,12 @@
       <c r="D210" t="n">
         <v>97</v>
       </c>
+      <c r="E210" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="F210" t="n">
+        <v>27.39</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4637,6 +5901,12 @@
       <c r="D211" t="n">
         <v>71</v>
       </c>
+      <c r="E211" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="F211" t="n">
+        <v>22.39</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4657,6 +5927,12 @@
       <c r="D212" t="n">
         <v>111</v>
       </c>
+      <c r="E212" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="F212" t="n">
+        <v>32.17</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4677,6 +5953,12 @@
       <c r="D213" t="n">
         <v>114</v>
       </c>
+      <c r="E213" t="n">
+        <v>179.66</v>
+      </c>
+      <c r="F213" t="n">
+        <v>83.75</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4697,6 +5979,12 @@
       <c r="D214" t="n">
         <v>126</v>
       </c>
+      <c r="E214" t="n">
+        <v>185.69</v>
+      </c>
+      <c r="F214" t="n">
+        <v>51.99</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4717,6 +6005,12 @@
       <c r="D215" t="n">
         <v>122</v>
       </c>
+      <c r="E215" t="n">
+        <v>179.42</v>
+      </c>
+      <c r="F215" t="n">
+        <v>23.59</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4737,6 +6031,12 @@
       <c r="D216" t="n">
         <v>75</v>
       </c>
+      <c r="E216" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="F216" t="n">
+        <v>65.76000000000001</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4757,6 +6057,12 @@
       <c r="D217" t="n">
         <v>97</v>
       </c>
+      <c r="E217" t="n">
+        <v>109.79</v>
+      </c>
+      <c r="F217" t="n">
+        <v>78.84999999999999</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4777,6 +6083,12 @@
       <c r="D218" t="n">
         <v>97</v>
       </c>
+      <c r="E218" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="F218" t="n">
+        <v>82.04000000000001</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4797,6 +6109,12 @@
       <c r="D219" t="n">
         <v>113</v>
       </c>
+      <c r="E219" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F219" t="n">
+        <v>101.27</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4817,6 +6135,12 @@
       <c r="D220" t="n">
         <v>113</v>
       </c>
+      <c r="E220" t="n">
+        <v>168.57</v>
+      </c>
+      <c r="F220" t="n">
+        <v>31.69</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4837,6 +6161,12 @@
       <c r="D221" t="n">
         <v>89</v>
       </c>
+      <c r="E221" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="F221" t="n">
+        <v>39.8</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4857,6 +6187,12 @@
       <c r="D222" t="n">
         <v>99</v>
       </c>
+      <c r="E222" t="n">
+        <v>158.38</v>
+      </c>
+      <c r="F222" t="n">
+        <v>71.15000000000001</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4877,6 +6213,12 @@
       <c r="D223" t="n">
         <v>80</v>
       </c>
+      <c r="E223" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="F223" t="n">
+        <v>53.76</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4897,6 +6239,12 @@
       <c r="D224" t="n">
         <v>127</v>
       </c>
+      <c r="E224" t="n">
+        <v>158.03</v>
+      </c>
+      <c r="F224" t="n">
+        <v>33.71</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4917,6 +6265,12 @@
       <c r="D225" t="n">
         <v>124</v>
       </c>
+      <c r="E225" t="n">
+        <v>175.48</v>
+      </c>
+      <c r="F225" t="n">
+        <v>94.47</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4937,6 +6291,12 @@
       <c r="D226" t="n">
         <v>97</v>
       </c>
+      <c r="E226" t="n">
+        <v>150.91</v>
+      </c>
+      <c r="F226" t="n">
+        <v>30.88</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4957,6 +6317,12 @@
       <c r="D227" t="n">
         <v>94</v>
       </c>
+      <c r="E227" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="F227" t="n">
+        <v>29.88</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4977,6 +6343,12 @@
       <c r="D228" t="n">
         <v>108</v>
       </c>
+      <c r="E228" t="n">
+        <v>107.77</v>
+      </c>
+      <c r="F228" t="n">
+        <v>59.69</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4997,6 +6369,12 @@
       <c r="D229" t="n">
         <v>102</v>
       </c>
+      <c r="E229" t="n">
+        <v>118.36</v>
+      </c>
+      <c r="F229" t="n">
+        <v>60.66</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5017,6 +6395,12 @@
       <c r="D230" t="n">
         <v>70</v>
       </c>
+      <c r="E230" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="F230" t="n">
+        <v>40.95</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5037,6 +6421,12 @@
       <c r="D231" t="n">
         <v>126</v>
       </c>
+      <c r="E231" t="n">
+        <v>196.97</v>
+      </c>
+      <c r="F231" t="n">
+        <v>27.55</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5057,6 +6447,12 @@
       <c r="D232" t="n">
         <v>96</v>
       </c>
+      <c r="E232" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="F232" t="n">
+        <v>77.58</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5077,6 +6473,12 @@
       <c r="D233" t="n">
         <v>126</v>
       </c>
+      <c r="E233" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="F233" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5097,6 +6499,12 @@
       <c r="D234" t="n">
         <v>121</v>
       </c>
+      <c r="E234" t="n">
+        <v>161.82</v>
+      </c>
+      <c r="F234" t="n">
+        <v>29.9</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5117,6 +6525,12 @@
       <c r="D235" t="n">
         <v>82</v>
       </c>
+      <c r="E235" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="F235" t="n">
+        <v>66.95999999999999</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5137,6 +6551,12 @@
       <c r="D236" t="n">
         <v>110</v>
       </c>
+      <c r="E236" t="n">
+        <v>119.52</v>
+      </c>
+      <c r="F236" t="n">
+        <v>95.34</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5157,6 +6577,12 @@
       <c r="D237" t="n">
         <v>72</v>
       </c>
+      <c r="E237" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="F237" t="n">
+        <v>57.35</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5177,6 +6603,12 @@
       <c r="D238" t="n">
         <v>108</v>
       </c>
+      <c r="E238" t="n">
+        <v>144.42</v>
+      </c>
+      <c r="F238" t="n">
+        <v>81.77</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5197,6 +6629,12 @@
       <c r="D239" t="n">
         <v>75</v>
       </c>
+      <c r="E239" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="F239" t="n">
+        <v>48.11</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5217,6 +6655,12 @@
       <c r="D240" t="n">
         <v>77</v>
       </c>
+      <c r="E240" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="F240" t="n">
+        <v>43.36</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5237,6 +6681,12 @@
       <c r="D241" t="n">
         <v>96</v>
       </c>
+      <c r="E241" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="F241" t="n">
+        <v>20.66</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5257,6 +6707,12 @@
       <c r="D242" t="n">
         <v>78</v>
       </c>
+      <c r="E242" t="n">
+        <v>115.58</v>
+      </c>
+      <c r="F242" t="n">
+        <v>35.59</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5277,6 +6733,12 @@
       <c r="D243" t="n">
         <v>106</v>
       </c>
+      <c r="E243" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="F243" t="n">
+        <v>45.53</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5297,6 +6759,12 @@
       <c r="D244" t="n">
         <v>102</v>
       </c>
+      <c r="E244" t="n">
+        <v>127.37</v>
+      </c>
+      <c r="F244" t="n">
+        <v>35.17</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5317,6 +6785,12 @@
       <c r="D245" t="n">
         <v>120</v>
       </c>
+      <c r="E245" t="n">
+        <v>180.16</v>
+      </c>
+      <c r="F245" t="n">
+        <v>83.11</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5337,6 +6811,12 @@
       <c r="D246" t="n">
         <v>111</v>
       </c>
+      <c r="E246" t="n">
+        <v>124.63</v>
+      </c>
+      <c r="F246" t="n">
+        <v>57.93</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5357,6 +6837,12 @@
       <c r="D247" t="n">
         <v>113</v>
       </c>
+      <c r="E247" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="F247" t="n">
+        <v>23.82</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5377,6 +6863,12 @@
       <c r="D248" t="n">
         <v>93</v>
       </c>
+      <c r="E248" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="F248" t="n">
+        <v>29.31</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5397,6 +6889,12 @@
       <c r="D249" t="n">
         <v>84</v>
       </c>
+      <c r="E249" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="F249" t="n">
+        <v>55.65</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5417,6 +6915,12 @@
       <c r="D250" t="n">
         <v>128</v>
       </c>
+      <c r="E250" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="F250" t="n">
+        <v>26.51</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5437,6 +6941,12 @@
       <c r="D251" t="n">
         <v>123</v>
       </c>
+      <c r="E251" t="n">
+        <v>167.68</v>
+      </c>
+      <c r="F251" t="n">
+        <v>96.97</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5457,6 +6967,12 @@
       <c r="D252" t="n">
         <v>101</v>
       </c>
+      <c r="E252" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="F252" t="n">
+        <v>52.66</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5477,6 +6993,12 @@
       <c r="D253" t="n">
         <v>101</v>
       </c>
+      <c r="E253" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="F253" t="n">
+        <v>51.55</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5497,6 +7019,12 @@
       <c r="D254" t="n">
         <v>93</v>
       </c>
+      <c r="E254" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="F254" t="n">
+        <v>55.27</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5517,6 +7045,12 @@
       <c r="D255" t="n">
         <v>110</v>
       </c>
+      <c r="E255" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="F255" t="n">
+        <v>84.54000000000001</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5537,6 +7071,12 @@
       <c r="D256" t="n">
         <v>121</v>
       </c>
+      <c r="E256" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="F256" t="n">
+        <v>49.71</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5557,6 +7097,12 @@
       <c r="D257" t="n">
         <v>118</v>
       </c>
+      <c r="E257" t="n">
+        <v>131.43</v>
+      </c>
+      <c r="F257" t="n">
+        <v>77.7</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5577,6 +7123,12 @@
       <c r="D258" t="n">
         <v>118</v>
       </c>
+      <c r="E258" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="F258" t="n">
+        <v>67.77</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5597,6 +7149,12 @@
       <c r="D259" t="n">
         <v>127</v>
       </c>
+      <c r="E259" t="n">
+        <v>193.46</v>
+      </c>
+      <c r="F259" t="n">
+        <v>44.48</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5617,6 +7175,12 @@
       <c r="D260" t="n">
         <v>121</v>
       </c>
+      <c r="E260" t="n">
+        <v>130.51</v>
+      </c>
+      <c r="F260" t="n">
+        <v>97.89</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5637,6 +7201,12 @@
       <c r="D261" t="n">
         <v>81</v>
       </c>
+      <c r="E261" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="F261" t="n">
+        <v>60.59</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5657,6 +7227,12 @@
       <c r="D262" t="n">
         <v>108</v>
       </c>
+      <c r="E262" t="n">
+        <v>154.11</v>
+      </c>
+      <c r="F262" t="n">
+        <v>69.53</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5677,6 +7253,12 @@
       <c r="D263" t="n">
         <v>71</v>
       </c>
+      <c r="E263" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="F263" t="n">
+        <v>55.94</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5697,6 +7279,12 @@
       <c r="D264" t="n">
         <v>72</v>
       </c>
+      <c r="E264" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="F264" t="n">
+        <v>57.63</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5717,6 +7305,12 @@
       <c r="D265" t="n">
         <v>118</v>
       </c>
+      <c r="E265" t="n">
+        <v>175.81</v>
+      </c>
+      <c r="F265" t="n">
+        <v>80.39</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5737,6 +7331,12 @@
       <c r="D266" t="n">
         <v>106</v>
       </c>
+      <c r="E266" t="n">
+        <v>165.32</v>
+      </c>
+      <c r="F266" t="n">
+        <v>82.44</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5757,6 +7357,12 @@
       <c r="D267" t="n">
         <v>118</v>
       </c>
+      <c r="E267" t="n">
+        <v>108.28</v>
+      </c>
+      <c r="F267" t="n">
+        <v>79.43000000000001</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5777,6 +7383,12 @@
       <c r="D268" t="n">
         <v>125</v>
       </c>
+      <c r="E268" t="n">
+        <v>192.66</v>
+      </c>
+      <c r="F268" t="n">
+        <v>82.51000000000001</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5797,6 +7409,12 @@
       <c r="D269" t="n">
         <v>86</v>
       </c>
+      <c r="E269" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="F269" t="n">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5817,6 +7435,12 @@
       <c r="D270" t="n">
         <v>128</v>
       </c>
+      <c r="E270" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="F270" t="n">
+        <v>91.45999999999999</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5837,6 +7461,12 @@
       <c r="D271" t="n">
         <v>118</v>
       </c>
+      <c r="E271" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="F271" t="n">
+        <v>31.74</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5857,6 +7487,12 @@
       <c r="D272" t="n">
         <v>71</v>
       </c>
+      <c r="E272" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="F272" t="n">
+        <v>57.56</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5877,6 +7513,12 @@
       <c r="D273" t="n">
         <v>71</v>
       </c>
+      <c r="E273" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="F273" t="n">
+        <v>57.08</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5897,6 +7539,12 @@
       <c r="D274" t="n">
         <v>97</v>
       </c>
+      <c r="E274" t="n">
+        <v>103.11</v>
+      </c>
+      <c r="F274" t="n">
+        <v>16.68</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5917,6 +7565,12 @@
       <c r="D275" t="n">
         <v>123</v>
       </c>
+      <c r="E275" t="n">
+        <v>160.73</v>
+      </c>
+      <c r="F275" t="n">
+        <v>94.63</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5937,6 +7591,12 @@
       <c r="D276" t="n">
         <v>92</v>
       </c>
+      <c r="E276" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="F276" t="n">
+        <v>22.69</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5957,6 +7617,12 @@
       <c r="D277" t="n">
         <v>106</v>
       </c>
+      <c r="E277" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="F277" t="n">
+        <v>42.54</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5977,6 +7643,12 @@
       <c r="D278" t="n">
         <v>101</v>
       </c>
+      <c r="E278" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F278" t="n">
+        <v>71.47</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5997,6 +7669,12 @@
       <c r="D279" t="n">
         <v>102</v>
       </c>
+      <c r="E279" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="F279" t="n">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6017,6 +7695,12 @@
       <c r="D280" t="n">
         <v>70</v>
       </c>
+      <c r="E280" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="F280" t="n">
+        <v>53.44</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6037,6 +7721,12 @@
       <c r="D281" t="n">
         <v>88</v>
       </c>
+      <c r="E281" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="F281" t="n">
+        <v>68.12</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6057,6 +7747,12 @@
       <c r="D282" t="n">
         <v>71</v>
       </c>
+      <c r="E282" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="F282" t="n">
+        <v>37.67</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6077,6 +7773,12 @@
       <c r="D283" t="n">
         <v>122</v>
       </c>
+      <c r="E283" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="F283" t="n">
+        <v>18.88</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6097,6 +7799,12 @@
       <c r="D284" t="n">
         <v>113</v>
       </c>
+      <c r="E284" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="F284" t="n">
+        <v>41.28</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6117,6 +7825,12 @@
       <c r="D285" t="n">
         <v>95</v>
       </c>
+      <c r="E285" t="n">
+        <v>144.16</v>
+      </c>
+      <c r="F285" t="n">
+        <v>58.21</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6137,6 +7851,12 @@
       <c r="D286" t="n">
         <v>101</v>
       </c>
+      <c r="E286" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="F286" t="n">
+        <v>89.47</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6157,6 +7877,12 @@
       <c r="D287" t="n">
         <v>75</v>
       </c>
+      <c r="E287" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="F287" t="n">
+        <v>46.79</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6177,6 +7903,12 @@
       <c r="D288" t="n">
         <v>101</v>
       </c>
+      <c r="E288" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="F288" t="n">
+        <v>34.83</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6197,6 +7929,12 @@
       <c r="D289" t="n">
         <v>124</v>
       </c>
+      <c r="E289" t="n">
+        <v>118.28</v>
+      </c>
+      <c r="F289" t="n">
+        <v>77.56</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6217,6 +7955,12 @@
       <c r="D290" t="n">
         <v>73</v>
       </c>
+      <c r="E290" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="F290" t="n">
+        <v>40.51</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6237,6 +7981,12 @@
       <c r="D291" t="n">
         <v>124</v>
       </c>
+      <c r="E291" t="n">
+        <v>115.96</v>
+      </c>
+      <c r="F291" t="n">
+        <v>91.13</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6257,6 +8007,12 @@
       <c r="D292" t="n">
         <v>80</v>
       </c>
+      <c r="E292" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="F292" t="n">
+        <v>18.42</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6277,6 +8033,12 @@
       <c r="D293" t="n">
         <v>125</v>
       </c>
+      <c r="E293" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="F293" t="n">
+        <v>90.09999999999999</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6297,6 +8059,12 @@
       <c r="D294" t="n">
         <v>128</v>
       </c>
+      <c r="E294" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="F294" t="n">
+        <v>71.16</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6317,6 +8085,12 @@
       <c r="D295" t="n">
         <v>86</v>
       </c>
+      <c r="E295" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F295" t="n">
+        <v>75.01000000000001</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6337,6 +8111,12 @@
       <c r="D296" t="n">
         <v>107</v>
       </c>
+      <c r="E296" t="n">
+        <v>125.04</v>
+      </c>
+      <c r="F296" t="n">
+        <v>43.49</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6357,6 +8137,12 @@
       <c r="D297" t="n">
         <v>93</v>
       </c>
+      <c r="E297" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="F297" t="n">
+        <v>58.08</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6377,6 +8163,12 @@
       <c r="D298" t="n">
         <v>74</v>
       </c>
+      <c r="E298" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="F298" t="n">
+        <v>62.83</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6397,6 +8189,12 @@
       <c r="D299" t="n">
         <v>121</v>
       </c>
+      <c r="E299" t="n">
+        <v>145.53</v>
+      </c>
+      <c r="F299" t="n">
+        <v>27.45</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6417,6 +8215,12 @@
       <c r="D300" t="n">
         <v>103</v>
       </c>
+      <c r="E300" t="n">
+        <v>139.29</v>
+      </c>
+      <c r="F300" t="n">
+        <v>87.84999999999999</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6437,6 +8241,12 @@
       <c r="D301" t="n">
         <v>75</v>
       </c>
+      <c r="E301" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="F301" t="n">
+        <v>49.94</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6457,6 +8267,12 @@
       <c r="D302" t="n">
         <v>91</v>
       </c>
+      <c r="E302" t="n">
+        <v>131</v>
+      </c>
+      <c r="F302" t="n">
+        <v>18.28</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6477,6 +8293,12 @@
       <c r="D303" t="n">
         <v>80</v>
       </c>
+      <c r="E303" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="F303" t="n">
+        <v>30.06</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6497,6 +8319,12 @@
       <c r="D304" t="n">
         <v>117</v>
       </c>
+      <c r="E304" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="F304" t="n">
+        <v>79.69</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6517,6 +8345,12 @@
       <c r="D305" t="n">
         <v>85</v>
       </c>
+      <c r="E305" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="F305" t="n">
+        <v>17.04</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6537,6 +8371,12 @@
       <c r="D306" t="n">
         <v>102</v>
       </c>
+      <c r="E306" t="n">
+        <v>156.74</v>
+      </c>
+      <c r="F306" t="n">
+        <v>59.84</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6557,6 +8397,12 @@
       <c r="D307" t="n">
         <v>78</v>
       </c>
+      <c r="E307" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="F307" t="n">
+        <v>31.93</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6577,6 +8423,12 @@
       <c r="D308" t="n">
         <v>129</v>
       </c>
+      <c r="E308" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="F308" t="n">
+        <v>79.42</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6597,6 +8449,12 @@
       <c r="D309" t="n">
         <v>128</v>
       </c>
+      <c r="E309" t="n">
+        <v>184.96</v>
+      </c>
+      <c r="F309" t="n">
+        <v>23.59</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6617,6 +8475,12 @@
       <c r="D310" t="n">
         <v>75</v>
       </c>
+      <c r="E310" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="F310" t="n">
+        <v>60.27</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6637,6 +8501,12 @@
       <c r="D311" t="n">
         <v>85</v>
       </c>
+      <c r="E311" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="F311" t="n">
+        <v>74.81</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6657,6 +8527,12 @@
       <c r="D312" t="n">
         <v>98</v>
       </c>
+      <c r="E312" t="n">
+        <v>94.81</v>
+      </c>
+      <c r="F312" t="n">
+        <v>85.91</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6677,6 +8553,12 @@
       <c r="D313" t="n">
         <v>72</v>
       </c>
+      <c r="E313" t="n">
+        <v>78.94</v>
+      </c>
+      <c r="F313" t="n">
+        <v>51.28</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6697,6 +8579,12 @@
       <c r="D314" t="n">
         <v>89</v>
       </c>
+      <c r="E314" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="F314" t="n">
+        <v>22.03</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6717,6 +8605,12 @@
       <c r="D315" t="n">
         <v>129</v>
       </c>
+      <c r="E315" t="n">
+        <v>167</v>
+      </c>
+      <c r="F315" t="n">
+        <v>92.70999999999999</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6737,6 +8631,12 @@
       <c r="D316" t="n">
         <v>128</v>
       </c>
+      <c r="E316" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="F316" t="n">
+        <v>21.56</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6757,6 +8657,12 @@
       <c r="D317" t="n">
         <v>105</v>
       </c>
+      <c r="E317" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="F317" t="n">
+        <v>17.49</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6777,6 +8683,12 @@
       <c r="D318" t="n">
         <v>88</v>
       </c>
+      <c r="E318" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="F318" t="n">
+        <v>34.56</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6797,6 +8709,12 @@
       <c r="D319" t="n">
         <v>95</v>
       </c>
+      <c r="E319" t="n">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="F319" t="n">
+        <v>49.07</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6817,6 +8735,12 @@
       <c r="D320" t="n">
         <v>72</v>
       </c>
+      <c r="E320" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="F320" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6837,6 +8761,12 @@
       <c r="D321" t="n">
         <v>88</v>
       </c>
+      <c r="E321" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="F321" t="n">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6857,6 +8787,12 @@
       <c r="D322" t="n">
         <v>89</v>
       </c>
+      <c r="E322" t="n">
+        <v>134.94</v>
+      </c>
+      <c r="F322" t="n">
+        <v>43.11</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6877,6 +8813,12 @@
       <c r="D323" t="n">
         <v>101</v>
       </c>
+      <c r="E323" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="F323" t="n">
+        <v>35.88</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6897,6 +8839,12 @@
       <c r="D324" t="n">
         <v>76</v>
       </c>
+      <c r="E324" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="F324" t="n">
+        <v>68.23999999999999</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6917,6 +8865,12 @@
       <c r="D325" t="n">
         <v>121</v>
       </c>
+      <c r="E325" t="n">
+        <v>107.17</v>
+      </c>
+      <c r="F325" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6937,6 +8891,12 @@
       <c r="D326" t="n">
         <v>110</v>
       </c>
+      <c r="E326" t="n">
+        <v>127.37</v>
+      </c>
+      <c r="F326" t="n">
+        <v>53.74</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6957,6 +8917,12 @@
       <c r="D327" t="n">
         <v>102</v>
       </c>
+      <c r="E327" t="n">
+        <v>125.06</v>
+      </c>
+      <c r="F327" t="n">
+        <v>27.82</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6977,6 +8943,12 @@
       <c r="D328" t="n">
         <v>109</v>
       </c>
+      <c r="E328" t="n">
+        <v>108.34</v>
+      </c>
+      <c r="F328" t="n">
+        <v>81.33</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6997,6 +8969,12 @@
       <c r="D329" t="n">
         <v>108</v>
       </c>
+      <c r="E329" t="n">
+        <v>109.66</v>
+      </c>
+      <c r="F329" t="n">
+        <v>72.39</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7017,6 +8995,12 @@
       <c r="D330" t="n">
         <v>87</v>
       </c>
+      <c r="E330" t="n">
+        <v>95.86</v>
+      </c>
+      <c r="F330" t="n">
+        <v>27.46</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7037,6 +9021,12 @@
       <c r="D331" t="n">
         <v>109</v>
       </c>
+      <c r="E331" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="F331" t="n">
+        <v>23.08</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7057,6 +9047,12 @@
       <c r="D332" t="n">
         <v>70</v>
       </c>
+      <c r="E332" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="F332" t="n">
+        <v>46.23</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7077,6 +9073,12 @@
       <c r="D333" t="n">
         <v>80</v>
       </c>
+      <c r="E333" t="n">
+        <v>77.53</v>
+      </c>
+      <c r="F333" t="n">
+        <v>51.27</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7097,6 +9099,12 @@
       <c r="D334" t="n">
         <v>97</v>
       </c>
+      <c r="E334" t="n">
+        <v>103.01</v>
+      </c>
+      <c r="F334" t="n">
+        <v>34.43</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7117,6 +9125,12 @@
       <c r="D335" t="n">
         <v>126</v>
       </c>
+      <c r="E335" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="F335" t="n">
+        <v>108.76</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7137,6 +9151,12 @@
       <c r="D336" t="n">
         <v>94</v>
       </c>
+      <c r="E336" t="n">
+        <v>142.17</v>
+      </c>
+      <c r="F336" t="n">
+        <v>24.75</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7157,6 +9177,12 @@
       <c r="D337" t="n">
         <v>119</v>
       </c>
+      <c r="E337" t="n">
+        <v>151.71</v>
+      </c>
+      <c r="F337" t="n">
+        <v>56.44</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7177,6 +9203,12 @@
       <c r="D338" t="n">
         <v>92</v>
       </c>
+      <c r="E338" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="F338" t="n">
+        <v>78.91</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7197,6 +9229,12 @@
       <c r="D339" t="n">
         <v>100</v>
       </c>
+      <c r="E339" t="n">
+        <v>143.13</v>
+      </c>
+      <c r="F339" t="n">
+        <v>46.48</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7217,6 +9255,12 @@
       <c r="D340" t="n">
         <v>99</v>
       </c>
+      <c r="E340" t="n">
+        <v>118.68</v>
+      </c>
+      <c r="F340" t="n">
+        <v>62.26</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7237,6 +9281,12 @@
       <c r="D341" t="n">
         <v>111</v>
       </c>
+      <c r="E341" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="F341" t="n">
+        <v>49.75</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7257,6 +9307,12 @@
       <c r="D342" t="n">
         <v>104</v>
       </c>
+      <c r="E342" t="n">
+        <v>127.89</v>
+      </c>
+      <c r="F342" t="n">
+        <v>36.99</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7277,6 +9333,12 @@
       <c r="D343" t="n">
         <v>76</v>
       </c>
+      <c r="E343" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="F343" t="n">
+        <v>67.48999999999999</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7297,6 +9359,12 @@
       <c r="D344" t="n">
         <v>129</v>
       </c>
+      <c r="E344" t="n">
+        <v>180.13</v>
+      </c>
+      <c r="F344" t="n">
+        <v>58.95</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7317,6 +9385,12 @@
       <c r="D345" t="n">
         <v>85</v>
       </c>
+      <c r="E345" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="F345" t="n">
+        <v>69.75</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7337,6 +9411,12 @@
       <c r="D346" t="n">
         <v>95</v>
       </c>
+      <c r="E346" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F346" t="n">
+        <v>30.63</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7357,6 +9437,12 @@
       <c r="D347" t="n">
         <v>117</v>
       </c>
+      <c r="E347" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="F347" t="n">
+        <v>36.25</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7377,6 +9463,12 @@
       <c r="D348" t="n">
         <v>126</v>
       </c>
+      <c r="E348" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="F348" t="n">
+        <v>21.84</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7397,6 +9489,12 @@
       <c r="D349" t="n">
         <v>121</v>
       </c>
+      <c r="E349" t="n">
+        <v>159.32</v>
+      </c>
+      <c r="F349" t="n">
+        <v>77.29000000000001</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7417,6 +9515,12 @@
       <c r="D350" t="n">
         <v>129</v>
       </c>
+      <c r="E350" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="F350" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7437,6 +9541,12 @@
       <c r="D351" t="n">
         <v>118</v>
       </c>
+      <c r="E351" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="F351" t="n">
+        <v>94.2</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7457,6 +9567,12 @@
       <c r="D352" t="n">
         <v>71</v>
       </c>
+      <c r="E352" t="n">
+        <v>112.83</v>
+      </c>
+      <c r="F352" t="n">
+        <v>35.85</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7477,6 +9593,12 @@
       <c r="D353" t="n">
         <v>70</v>
       </c>
+      <c r="E353" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="F353" t="n">
+        <v>61.33</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7497,6 +9619,12 @@
       <c r="D354" t="n">
         <v>117</v>
       </c>
+      <c r="E354" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="F354" t="n">
+        <v>33.83</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7517,6 +9645,12 @@
       <c r="D355" t="n">
         <v>81</v>
       </c>
+      <c r="E355" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F355" t="n">
+        <v>64.92</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7537,6 +9671,12 @@
       <c r="D356" t="n">
         <v>74</v>
       </c>
+      <c r="E356" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="F356" t="n">
+        <v>54.2</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7557,6 +9697,12 @@
       <c r="D357" t="n">
         <v>106</v>
       </c>
+      <c r="E357" t="n">
+        <v>105.66</v>
+      </c>
+      <c r="F357" t="n">
+        <v>77.19</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7577,6 +9723,12 @@
       <c r="D358" t="n">
         <v>101</v>
       </c>
+      <c r="E358" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="F358" t="n">
+        <v>79.14</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7597,6 +9749,12 @@
       <c r="D359" t="n">
         <v>128</v>
       </c>
+      <c r="E359" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F359" t="n">
+        <v>92.26000000000001</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7617,6 +9775,12 @@
       <c r="D360" t="n">
         <v>124</v>
       </c>
+      <c r="E360" t="n">
+        <v>127.48</v>
+      </c>
+      <c r="F360" t="n">
+        <v>76.84</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7637,6 +9801,12 @@
       <c r="D361" t="n">
         <v>78</v>
       </c>
+      <c r="E361" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="F361" t="n">
+        <v>19.38</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7657,6 +9827,12 @@
       <c r="D362" t="n">
         <v>110</v>
       </c>
+      <c r="E362" t="n">
+        <v>166.92</v>
+      </c>
+      <c r="F362" t="n">
+        <v>19.18</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7677,6 +9853,12 @@
       <c r="D363" t="n">
         <v>104</v>
       </c>
+      <c r="E363" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="F363" t="n">
+        <v>87.43000000000001</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7697,6 +9879,12 @@
       <c r="D364" t="n">
         <v>88</v>
       </c>
+      <c r="E364" t="n">
+        <v>107.33</v>
+      </c>
+      <c r="F364" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -7717,6 +9905,12 @@
       <c r="D365" t="n">
         <v>117</v>
       </c>
+      <c r="E365" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="F365" t="n">
+        <v>87.45</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7737,6 +9931,12 @@
       <c r="D366" t="n">
         <v>85</v>
       </c>
+      <c r="E366" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="F366" t="n">
+        <v>43.45</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -7757,6 +9957,12 @@
       <c r="D367" t="n">
         <v>72</v>
       </c>
+      <c r="E367" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="F367" t="n">
+        <v>17.13</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -7777,6 +9983,12 @@
       <c r="D368" t="n">
         <v>89</v>
       </c>
+      <c r="E368" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="F368" t="n">
+        <v>21.71</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -7797,6 +10009,12 @@
       <c r="D369" t="n">
         <v>93</v>
       </c>
+      <c r="E369" t="n">
+        <v>146.53</v>
+      </c>
+      <c r="F369" t="n">
+        <v>61.77</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -7817,6 +10035,12 @@
       <c r="D370" t="n">
         <v>123</v>
       </c>
+      <c r="E370" t="n">
+        <v>183.57</v>
+      </c>
+      <c r="F370" t="n">
+        <v>58.15</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -7837,6 +10061,12 @@
       <c r="D371" t="n">
         <v>125</v>
       </c>
+      <c r="E371" t="n">
+        <v>181.71</v>
+      </c>
+      <c r="F371" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -7857,6 +10087,12 @@
       <c r="D372" t="n">
         <v>102</v>
       </c>
+      <c r="E372" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="F372" t="n">
+        <v>52.91</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -7877,6 +10113,12 @@
       <c r="D373" t="n">
         <v>93</v>
       </c>
+      <c r="E373" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="F373" t="n">
+        <v>18.43</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -7897,6 +10139,12 @@
       <c r="D374" t="n">
         <v>121</v>
       </c>
+      <c r="E374" t="n">
+        <v>161.52</v>
+      </c>
+      <c r="F374" t="n">
+        <v>70.95999999999999</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -7917,6 +10165,12 @@
       <c r="D375" t="n">
         <v>80</v>
       </c>
+      <c r="E375" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="F375" t="n">
+        <v>28.14</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -7937,6 +10191,12 @@
       <c r="D376" t="n">
         <v>118</v>
       </c>
+      <c r="E376" t="n">
+        <v>146.96</v>
+      </c>
+      <c r="F376" t="n">
+        <v>88.28</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7957,6 +10217,12 @@
       <c r="D377" t="n">
         <v>77</v>
       </c>
+      <c r="E377" t="n">
+        <v>96.81</v>
+      </c>
+      <c r="F377" t="n">
+        <v>29.47</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7977,6 +10243,12 @@
       <c r="D378" t="n">
         <v>105</v>
       </c>
+      <c r="E378" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="F378" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7997,6 +10269,12 @@
       <c r="D379" t="n">
         <v>107</v>
       </c>
+      <c r="E379" t="n">
+        <v>151.47</v>
+      </c>
+      <c r="F379" t="n">
+        <v>16.98</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8017,6 +10295,12 @@
       <c r="D380" t="n">
         <v>109</v>
       </c>
+      <c r="E380" t="n">
+        <v>103.51</v>
+      </c>
+      <c r="F380" t="n">
+        <v>22.27</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8037,6 +10321,12 @@
       <c r="D381" t="n">
         <v>89</v>
       </c>
+      <c r="E381" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="F381" t="n">
+        <v>39.55</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8057,6 +10347,12 @@
       <c r="D382" t="n">
         <v>104</v>
       </c>
+      <c r="E382" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="F382" t="n">
+        <v>53.04</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8077,6 +10373,12 @@
       <c r="D383" t="n">
         <v>117</v>
       </c>
+      <c r="E383" t="n">
+        <v>141.11</v>
+      </c>
+      <c r="F383" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8097,6 +10399,12 @@
       <c r="D384" t="n">
         <v>94</v>
       </c>
+      <c r="E384" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="F384" t="n">
+        <v>34.66</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8117,6 +10425,12 @@
       <c r="D385" t="n">
         <v>104</v>
       </c>
+      <c r="E385" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="F385" t="n">
+        <v>69.81</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8137,6 +10451,12 @@
       <c r="D386" t="n">
         <v>94</v>
       </c>
+      <c r="E386" t="n">
+        <v>121.12</v>
+      </c>
+      <c r="F386" t="n">
+        <v>74.73999999999999</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8157,6 +10477,12 @@
       <c r="D387" t="n">
         <v>98</v>
       </c>
+      <c r="E387" t="n">
+        <v>101.03</v>
+      </c>
+      <c r="F387" t="n">
+        <v>72.02</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8177,6 +10503,12 @@
       <c r="D388" t="n">
         <v>87</v>
       </c>
+      <c r="E388" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="F388" t="n">
+        <v>15.64</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8197,6 +10529,12 @@
       <c r="D389" t="n">
         <v>115</v>
       </c>
+      <c r="E389" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="F389" t="n">
+        <v>58.69</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8217,6 +10555,12 @@
       <c r="D390" t="n">
         <v>87</v>
       </c>
+      <c r="E390" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="F390" t="n">
+        <v>19.9</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -8237,6 +10581,12 @@
       <c r="D391" t="n">
         <v>71</v>
       </c>
+      <c r="E391" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="F391" t="n">
+        <v>23.54</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -8257,6 +10607,12 @@
       <c r="D392" t="n">
         <v>123</v>
       </c>
+      <c r="E392" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F392" t="n">
+        <v>109.47</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8277,6 +10633,12 @@
       <c r="D393" t="n">
         <v>104</v>
       </c>
+      <c r="E393" t="n">
+        <v>111.21</v>
+      </c>
+      <c r="F393" t="n">
+        <v>26.71</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -8297,6 +10659,12 @@
       <c r="D394" t="n">
         <v>85</v>
       </c>
+      <c r="E394" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="F394" t="n">
+        <v>44.55</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8317,6 +10685,12 @@
       <c r="D395" t="n">
         <v>130</v>
       </c>
+      <c r="E395" t="n">
+        <v>110.59</v>
+      </c>
+      <c r="F395" t="n">
+        <v>79.77</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8337,6 +10711,12 @@
       <c r="D396" t="n">
         <v>110</v>
       </c>
+      <c r="E396" t="n">
+        <v>175.12</v>
+      </c>
+      <c r="F396" t="n">
+        <v>74.45</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8357,6 +10737,12 @@
       <c r="D397" t="n">
         <v>105</v>
       </c>
+      <c r="E397" t="n">
+        <v>111.08</v>
+      </c>
+      <c r="F397" t="n">
+        <v>59.82</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8377,6 +10763,12 @@
       <c r="D398" t="n">
         <v>102</v>
       </c>
+      <c r="E398" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="F398" t="n">
+        <v>16.05</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8397,6 +10789,12 @@
       <c r="D399" t="n">
         <v>73</v>
       </c>
+      <c r="E399" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="F399" t="n">
+        <v>28.82</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8417,6 +10815,12 @@
       <c r="D400" t="n">
         <v>102</v>
       </c>
+      <c r="E400" t="n">
+        <v>137.21</v>
+      </c>
+      <c r="F400" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8437,6 +10841,12 @@
       <c r="D401" t="n">
         <v>83</v>
       </c>
+      <c r="E401" t="n">
+        <v>116.88</v>
+      </c>
+      <c r="F401" t="n">
+        <v>17.92</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8457,6 +10867,12 @@
       <c r="D402" t="n">
         <v>90</v>
       </c>
+      <c r="E402" t="n">
+        <v>114.89</v>
+      </c>
+      <c r="F402" t="n">
+        <v>37.17</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8477,6 +10893,12 @@
       <c r="D403" t="n">
         <v>117</v>
       </c>
+      <c r="E403" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="F403" t="n">
+        <v>20.46</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8497,6 +10919,12 @@
       <c r="D404" t="n">
         <v>89</v>
       </c>
+      <c r="E404" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="F404" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8517,6 +10945,12 @@
       <c r="D405" t="n">
         <v>125</v>
       </c>
+      <c r="E405" t="n">
+        <v>134.89</v>
+      </c>
+      <c r="F405" t="n">
+        <v>55.96</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8537,6 +10971,12 @@
       <c r="D406" t="n">
         <v>77</v>
       </c>
+      <c r="E406" t="n">
+        <v>118.86</v>
+      </c>
+      <c r="F406" t="n">
+        <v>19.21</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8557,6 +10997,12 @@
       <c r="D407" t="n">
         <v>76</v>
       </c>
+      <c r="E407" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="F407" t="n">
+        <v>43.75</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -8577,6 +11023,12 @@
       <c r="D408" t="n">
         <v>72</v>
       </c>
+      <c r="E408" t="n">
+        <v>113.19</v>
+      </c>
+      <c r="F408" t="n">
+        <v>48.03</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -8597,6 +11049,12 @@
       <c r="D409" t="n">
         <v>86</v>
       </c>
+      <c r="E409" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="F409" t="n">
+        <v>64.54000000000001</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -8617,6 +11075,12 @@
       <c r="D410" t="n">
         <v>102</v>
       </c>
+      <c r="E410" t="n">
+        <v>141.24</v>
+      </c>
+      <c r="F410" t="n">
+        <v>30.61</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -8637,6 +11101,12 @@
       <c r="D411" t="n">
         <v>117</v>
       </c>
+      <c r="E411" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="F411" t="n">
+        <v>32.25</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -8657,6 +11127,12 @@
       <c r="D412" t="n">
         <v>81</v>
       </c>
+      <c r="E412" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="F412" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -8677,6 +11153,12 @@
       <c r="D413" t="n">
         <v>128</v>
       </c>
+      <c r="E413" t="n">
+        <v>109.21</v>
+      </c>
+      <c r="F413" t="n">
+        <v>80.3</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -8697,6 +11179,12 @@
       <c r="D414" t="n">
         <v>120</v>
       </c>
+      <c r="E414" t="n">
+        <v>167.15</v>
+      </c>
+      <c r="F414" t="n">
+        <v>81.58</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8717,6 +11205,12 @@
       <c r="D415" t="n">
         <v>91</v>
       </c>
+      <c r="E415" t="n">
+        <v>114.62</v>
+      </c>
+      <c r="F415" t="n">
+        <v>15.81</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -8737,6 +11231,12 @@
       <c r="D416" t="n">
         <v>124</v>
       </c>
+      <c r="E416" t="n">
+        <v>182.71</v>
+      </c>
+      <c r="F416" t="n">
+        <v>105.67</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -8757,6 +11257,12 @@
       <c r="D417" t="n">
         <v>91</v>
       </c>
+      <c r="E417" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="F417" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8777,6 +11283,12 @@
       <c r="D418" t="n">
         <v>115</v>
       </c>
+      <c r="E418" t="n">
+        <v>165.16</v>
+      </c>
+      <c r="F418" t="n">
+        <v>63.94</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8797,6 +11309,12 @@
       <c r="D419" t="n">
         <v>99</v>
       </c>
+      <c r="E419" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="F419" t="n">
+        <v>67.5</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8817,6 +11335,12 @@
       <c r="D420" t="n">
         <v>107</v>
       </c>
+      <c r="E420" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="F420" t="n">
+        <v>85.95</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8837,6 +11361,12 @@
       <c r="D421" t="n">
         <v>107</v>
       </c>
+      <c r="E421" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="F421" t="n">
+        <v>73.36</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8857,6 +11387,12 @@
       <c r="D422" t="n">
         <v>114</v>
       </c>
+      <c r="E422" t="n">
+        <v>165.49</v>
+      </c>
+      <c r="F422" t="n">
+        <v>85.65000000000001</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8877,6 +11413,12 @@
       <c r="D423" t="n">
         <v>120</v>
       </c>
+      <c r="E423" t="n">
+        <v>159.86</v>
+      </c>
+      <c r="F423" t="n">
+        <v>48.55</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8897,6 +11439,12 @@
       <c r="D424" t="n">
         <v>123</v>
       </c>
+      <c r="E424" t="n">
+        <v>149.87</v>
+      </c>
+      <c r="F424" t="n">
+        <v>93.62</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8917,6 +11465,12 @@
       <c r="D425" t="n">
         <v>77</v>
       </c>
+      <c r="E425" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F425" t="n">
+        <v>16.18</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8937,6 +11491,12 @@
       <c r="D426" t="n">
         <v>96</v>
       </c>
+      <c r="E426" t="n">
+        <v>144.17</v>
+      </c>
+      <c r="F426" t="n">
+        <v>78.83</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8957,6 +11517,12 @@
       <c r="D427" t="n">
         <v>96</v>
       </c>
+      <c r="E427" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="F427" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8977,6 +11543,12 @@
       <c r="D428" t="n">
         <v>103</v>
       </c>
+      <c r="E428" t="n">
+        <v>149.69</v>
+      </c>
+      <c r="F428" t="n">
+        <v>78.59</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8997,6 +11569,12 @@
       <c r="D429" t="n">
         <v>90</v>
       </c>
+      <c r="E429" t="n">
+        <v>103.62</v>
+      </c>
+      <c r="F429" t="n">
+        <v>44.03</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9017,6 +11595,12 @@
       <c r="D430" t="n">
         <v>99</v>
       </c>
+      <c r="E430" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="F430" t="n">
+        <v>62.64</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9037,6 +11621,12 @@
       <c r="D431" t="n">
         <v>102</v>
       </c>
+      <c r="E431" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="F431" t="n">
+        <v>55.57</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9057,6 +11647,12 @@
       <c r="D432" t="n">
         <v>97</v>
       </c>
+      <c r="E432" t="n">
+        <v>100.99</v>
+      </c>
+      <c r="F432" t="n">
+        <v>67.77</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9077,6 +11673,12 @@
       <c r="D433" t="n">
         <v>116</v>
       </c>
+      <c r="E433" t="n">
+        <v>162.18</v>
+      </c>
+      <c r="F433" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9097,6 +11699,12 @@
       <c r="D434" t="n">
         <v>102</v>
       </c>
+      <c r="E434" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="F434" t="n">
+        <v>19.92</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9117,6 +11725,12 @@
       <c r="D435" t="n">
         <v>74</v>
       </c>
+      <c r="E435" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="F435" t="n">
+        <v>24.81</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9137,6 +11751,12 @@
       <c r="D436" t="n">
         <v>129</v>
       </c>
+      <c r="E436" t="n">
+        <v>196.04</v>
+      </c>
+      <c r="F436" t="n">
+        <v>34.79</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9157,6 +11777,12 @@
       <c r="D437" t="n">
         <v>130</v>
       </c>
+      <c r="E437" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="F437" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9177,6 +11803,12 @@
       <c r="D438" t="n">
         <v>117</v>
       </c>
+      <c r="E438" t="n">
+        <v>144.48</v>
+      </c>
+      <c r="F438" t="n">
+        <v>36.79</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9197,6 +11829,12 @@
       <c r="D439" t="n">
         <v>88</v>
       </c>
+      <c r="E439" t="n">
+        <v>134.22</v>
+      </c>
+      <c r="F439" t="n">
+        <v>77.61</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9217,6 +11855,12 @@
       <c r="D440" t="n">
         <v>73</v>
       </c>
+      <c r="E440" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="F440" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9237,6 +11881,12 @@
       <c r="D441" t="n">
         <v>104</v>
       </c>
+      <c r="E441" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="F441" t="n">
+        <v>29.81</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9257,6 +11907,12 @@
       <c r="D442" t="n">
         <v>118</v>
       </c>
+      <c r="E442" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="F442" t="n">
+        <v>87.59</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9277,6 +11933,12 @@
       <c r="D443" t="n">
         <v>86</v>
       </c>
+      <c r="E443" t="n">
+        <v>111.99</v>
+      </c>
+      <c r="F443" t="n">
+        <v>55.39</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -9297,6 +11959,12 @@
       <c r="D444" t="n">
         <v>113</v>
       </c>
+      <c r="E444" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="F444" t="n">
+        <v>59.17</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -9317,6 +11985,12 @@
       <c r="D445" t="n">
         <v>97</v>
       </c>
+      <c r="E445" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="F445" t="n">
+        <v>54.95</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -9337,6 +12011,12 @@
       <c r="D446" t="n">
         <v>99</v>
       </c>
+      <c r="E446" t="n">
+        <v>142.09</v>
+      </c>
+      <c r="F446" t="n">
+        <v>68.25</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -9357,6 +12037,12 @@
       <c r="D447" t="n">
         <v>98</v>
       </c>
+      <c r="E447" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="F447" t="n">
+        <v>31.49</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -9377,6 +12063,12 @@
       <c r="D448" t="n">
         <v>115</v>
       </c>
+      <c r="E448" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="F448" t="n">
+        <v>103.18</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -9397,6 +12089,12 @@
       <c r="D449" t="n">
         <v>122</v>
       </c>
+      <c r="E449" t="n">
+        <v>184.84</v>
+      </c>
+      <c r="F449" t="n">
+        <v>107.49</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -9417,6 +12115,12 @@
       <c r="D450" t="n">
         <v>75</v>
       </c>
+      <c r="E450" t="n">
+        <v>107.32</v>
+      </c>
+      <c r="F450" t="n">
+        <v>47.83</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -9437,6 +12141,12 @@
       <c r="D451" t="n">
         <v>104</v>
       </c>
+      <c r="E451" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="F451" t="n">
+        <v>31.16</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9457,6 +12167,12 @@
       <c r="D452" t="n">
         <v>129</v>
       </c>
+      <c r="E452" t="n">
+        <v>135.37</v>
+      </c>
+      <c r="F452" t="n">
+        <v>85.16</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9477,6 +12193,12 @@
       <c r="D453" t="n">
         <v>110</v>
       </c>
+      <c r="E453" t="n">
+        <v>109.87</v>
+      </c>
+      <c r="F453" t="n">
+        <v>22.46</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9497,6 +12219,12 @@
       <c r="D454" t="n">
         <v>106</v>
       </c>
+      <c r="E454" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="F454" t="n">
+        <v>18.34</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9517,6 +12245,12 @@
       <c r="D455" t="n">
         <v>93</v>
       </c>
+      <c r="E455" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="F455" t="n">
+        <v>31.92</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -9537,6 +12271,12 @@
       <c r="D456" t="n">
         <v>98</v>
       </c>
+      <c r="E456" t="n">
+        <v>123.08</v>
+      </c>
+      <c r="F456" t="n">
+        <v>48.7</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9557,6 +12297,12 @@
       <c r="D457" t="n">
         <v>118</v>
       </c>
+      <c r="E457" t="n">
+        <v>166.38</v>
+      </c>
+      <c r="F457" t="n">
+        <v>94.54000000000001</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9577,6 +12323,12 @@
       <c r="D458" t="n">
         <v>115</v>
       </c>
+      <c r="E458" t="n">
+        <v>172.66</v>
+      </c>
+      <c r="F458" t="n">
+        <v>79.97</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -9597,6 +12349,12 @@
       <c r="D459" t="n">
         <v>122</v>
       </c>
+      <c r="E459" t="n">
+        <v>130.99</v>
+      </c>
+      <c r="F459" t="n">
+        <v>86.26000000000001</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9617,6 +12375,12 @@
       <c r="D460" t="n">
         <v>100</v>
       </c>
+      <c r="E460" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="F460" t="n">
+        <v>46.91</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -9637,6 +12401,12 @@
       <c r="D461" t="n">
         <v>104</v>
       </c>
+      <c r="E461" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F461" t="n">
+        <v>42.58</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -9657,6 +12427,12 @@
       <c r="D462" t="n">
         <v>129</v>
       </c>
+      <c r="E462" t="n">
+        <v>190.55</v>
+      </c>
+      <c r="F462" t="n">
+        <v>55.25</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -9677,6 +12453,12 @@
       <c r="D463" t="n">
         <v>102</v>
       </c>
+      <c r="E463" t="n">
+        <v>92</v>
+      </c>
+      <c r="F463" t="n">
+        <v>90.86</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -9697,6 +12479,12 @@
       <c r="D464" t="n">
         <v>121</v>
       </c>
+      <c r="E464" t="n">
+        <v>135.26</v>
+      </c>
+      <c r="F464" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -9717,6 +12505,12 @@
       <c r="D465" t="n">
         <v>130</v>
       </c>
+      <c r="E465" t="n">
+        <v>186.92</v>
+      </c>
+      <c r="F465" t="n">
+        <v>104.04</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -9737,6 +12531,12 @@
       <c r="D466" t="n">
         <v>90</v>
       </c>
+      <c r="E466" t="n">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="F466" t="n">
+        <v>52.56</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -9757,6 +12557,12 @@
       <c r="D467" t="n">
         <v>101</v>
       </c>
+      <c r="E467" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="F467" t="n">
+        <v>48.38</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -9777,6 +12583,12 @@
       <c r="D468" t="n">
         <v>92</v>
       </c>
+      <c r="E468" t="n">
+        <v>126.76</v>
+      </c>
+      <c r="F468" t="n">
+        <v>63.84</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -9797,6 +12609,12 @@
       <c r="D469" t="n">
         <v>102</v>
       </c>
+      <c r="E469" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="F469" t="n">
+        <v>52.53</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -9817,6 +12635,12 @@
       <c r="D470" t="n">
         <v>72</v>
       </c>
+      <c r="E470" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="F470" t="n">
+        <v>57.96</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -9837,6 +12661,12 @@
       <c r="D471" t="n">
         <v>87</v>
       </c>
+      <c r="E471" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="F471" t="n">
+        <v>71.81999999999999</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -9857,6 +12687,12 @@
       <c r="D472" t="n">
         <v>94</v>
       </c>
+      <c r="E472" t="n">
+        <v>116.01</v>
+      </c>
+      <c r="F472" t="n">
+        <v>43.83</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -9877,6 +12713,12 @@
       <c r="D473" t="n">
         <v>111</v>
       </c>
+      <c r="E473" t="n">
+        <v>111.16</v>
+      </c>
+      <c r="F473" t="n">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -9897,6 +12739,12 @@
       <c r="D474" t="n">
         <v>100</v>
       </c>
+      <c r="E474" t="n">
+        <v>107.66</v>
+      </c>
+      <c r="F474" t="n">
+        <v>59.43</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -9917,6 +12765,12 @@
       <c r="D475" t="n">
         <v>123</v>
       </c>
+      <c r="E475" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F475" t="n">
+        <v>102.62</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9937,6 +12791,12 @@
       <c r="D476" t="n">
         <v>127</v>
       </c>
+      <c r="E476" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="F476" t="n">
+        <v>39.12</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9957,6 +12817,12 @@
       <c r="D477" t="n">
         <v>72</v>
       </c>
+      <c r="E477" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F477" t="n">
+        <v>44.44</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -9977,6 +12843,12 @@
       <c r="D478" t="n">
         <v>109</v>
       </c>
+      <c r="E478" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="F478" t="n">
+        <v>67.98</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9997,6 +12869,12 @@
       <c r="D479" t="n">
         <v>115</v>
       </c>
+      <c r="E479" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="F479" t="n">
+        <v>80.48</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10017,6 +12895,12 @@
       <c r="D480" t="n">
         <v>93</v>
       </c>
+      <c r="E480" t="n">
+        <v>144.88</v>
+      </c>
+      <c r="F480" t="n">
+        <v>23.13</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -10037,6 +12921,12 @@
       <c r="D481" t="n">
         <v>119</v>
       </c>
+      <c r="E481" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="F481" t="n">
+        <v>81.73999999999999</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10057,6 +12947,12 @@
       <c r="D482" t="n">
         <v>101</v>
       </c>
+      <c r="E482" t="n">
+        <v>128.17</v>
+      </c>
+      <c r="F482" t="n">
+        <v>84.01000000000001</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -10077,6 +12973,12 @@
       <c r="D483" t="n">
         <v>116</v>
       </c>
+      <c r="E483" t="n">
+        <v>139.75</v>
+      </c>
+      <c r="F483" t="n">
+        <v>33.03</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10097,6 +12999,12 @@
       <c r="D484" t="n">
         <v>91</v>
       </c>
+      <c r="E484" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="F484" t="n">
+        <v>29.86</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -10117,6 +13025,12 @@
       <c r="D485" t="n">
         <v>92</v>
       </c>
+      <c r="E485" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="F485" t="n">
+        <v>80.83</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -10137,6 +13051,12 @@
       <c r="D486" t="n">
         <v>71</v>
       </c>
+      <c r="E486" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="F486" t="n">
+        <v>20.29</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -10157,6 +13077,12 @@
       <c r="D487" t="n">
         <v>96</v>
       </c>
+      <c r="E487" t="n">
+        <v>148.39</v>
+      </c>
+      <c r="F487" t="n">
+        <v>75.92</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -10177,6 +13103,12 @@
       <c r="D488" t="n">
         <v>111</v>
       </c>
+      <c r="E488" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="F488" t="n">
+        <v>57.63</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -10197,6 +13129,12 @@
       <c r="D489" t="n">
         <v>71</v>
       </c>
+      <c r="E489" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="F489" t="n">
+        <v>23.82</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -10217,6 +13155,12 @@
       <c r="D490" t="n">
         <v>95</v>
       </c>
+      <c r="E490" t="n">
+        <v>146.11</v>
+      </c>
+      <c r="F490" t="n">
+        <v>76.29000000000001</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10237,6 +13181,12 @@
       <c r="D491" t="n">
         <v>86</v>
       </c>
+      <c r="E491" t="n">
+        <v>117.46</v>
+      </c>
+      <c r="F491" t="n">
+        <v>41.62</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10257,6 +13207,12 @@
       <c r="D492" t="n">
         <v>109</v>
       </c>
+      <c r="E492" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="F492" t="n">
+        <v>58.44</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10277,6 +13233,12 @@
       <c r="D493" t="n">
         <v>102</v>
       </c>
+      <c r="E493" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="F493" t="n">
+        <v>42.78</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10297,6 +13259,12 @@
       <c r="D494" t="n">
         <v>78</v>
       </c>
+      <c r="E494" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="F494" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -10317,6 +13285,12 @@
       <c r="D495" t="n">
         <v>112</v>
       </c>
+      <c r="E495" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="F495" t="n">
+        <v>30.54</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -10337,6 +13311,12 @@
       <c r="D496" t="n">
         <v>123</v>
       </c>
+      <c r="E496" t="n">
+        <v>170.87</v>
+      </c>
+      <c r="F496" t="n">
+        <v>54.53</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10357,6 +13337,12 @@
       <c r="D497" t="n">
         <v>117</v>
       </c>
+      <c r="E497" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="F497" t="n">
+        <v>102.62</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -10377,6 +13363,12 @@
       <c r="D498" t="n">
         <v>108</v>
       </c>
+      <c r="E498" t="n">
+        <v>166.37</v>
+      </c>
+      <c r="F498" t="n">
+        <v>37.11</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -10397,6 +13389,12 @@
       <c r="D499" t="n">
         <v>98</v>
       </c>
+      <c r="E499" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="F499" t="n">
+        <v>62.97</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10417,6 +13415,12 @@
       <c r="D500" t="n">
         <v>111</v>
       </c>
+      <c r="E500" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="F500" t="n">
+        <v>43.72</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -10437,6 +13441,12 @@
       <c r="D501" t="n">
         <v>124</v>
       </c>
+      <c r="E501" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="F501" t="n">
+        <v>90.53</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -10457,6 +13467,12 @@
       <c r="D502" t="n">
         <v>95</v>
       </c>
+      <c r="E502" t="n">
+        <v>139.76</v>
+      </c>
+      <c r="F502" t="n">
+        <v>23.57</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -10477,6 +13493,12 @@
       <c r="D503" t="n">
         <v>104</v>
       </c>
+      <c r="E503" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="F503" t="n">
+        <v>91.25</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -10497,6 +13519,12 @@
       <c r="D504" t="n">
         <v>119</v>
       </c>
+      <c r="E504" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="F504" t="n">
+        <v>58.35</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -10517,6 +13545,12 @@
       <c r="D505" t="n">
         <v>94</v>
       </c>
+      <c r="E505" t="n">
+        <v>140.62</v>
+      </c>
+      <c r="F505" t="n">
+        <v>30.74</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -10537,6 +13571,12 @@
       <c r="D506" t="n">
         <v>93</v>
       </c>
+      <c r="E506" t="n">
+        <v>113</v>
+      </c>
+      <c r="F506" t="n">
+        <v>19.08</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -10557,6 +13597,12 @@
       <c r="D507" t="n">
         <v>82</v>
       </c>
+      <c r="E507" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="F507" t="n">
+        <v>22.74</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -10577,6 +13623,12 @@
       <c r="D508" t="n">
         <v>129</v>
       </c>
+      <c r="E508" t="n">
+        <v>144.38</v>
+      </c>
+      <c r="F508" t="n">
+        <v>69.64</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -10597,6 +13649,12 @@
       <c r="D509" t="n">
         <v>127</v>
       </c>
+      <c r="E509" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="F509" t="n">
+        <v>51.15</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -10617,6 +13675,12 @@
       <c r="D510" t="n">
         <v>76</v>
       </c>
+      <c r="E510" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="F510" t="n">
+        <v>58.65</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -10637,6 +13701,12 @@
       <c r="D511" t="n">
         <v>126</v>
       </c>
+      <c r="E511" t="n">
+        <v>181.73</v>
+      </c>
+      <c r="F511" t="n">
+        <v>59.62</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -10657,6 +13727,12 @@
       <c r="D512" t="n">
         <v>105</v>
       </c>
+      <c r="E512" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="F512" t="n">
+        <v>35.34</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -10677,6 +13753,12 @@
       <c r="D513" t="n">
         <v>114</v>
       </c>
+      <c r="E513" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="F513" t="n">
+        <v>69.87</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -10697,6 +13779,12 @@
       <c r="D514" t="n">
         <v>89</v>
       </c>
+      <c r="E514" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="F514" t="n">
+        <v>60.53</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -10717,6 +13805,12 @@
       <c r="D515" t="n">
         <v>70</v>
       </c>
+      <c r="E515" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="F515" t="n">
+        <v>19.27</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -10737,6 +13831,12 @@
       <c r="D516" t="n">
         <v>77</v>
       </c>
+      <c r="E516" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="F516" t="n">
+        <v>21.23</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -10757,6 +13857,12 @@
       <c r="D517" t="n">
         <v>115</v>
       </c>
+      <c r="E517" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="F517" t="n">
+        <v>20.41</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -10777,6 +13883,12 @@
       <c r="D518" t="n">
         <v>85</v>
       </c>
+      <c r="E518" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="F518" t="n">
+        <v>59.7</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -10797,6 +13909,12 @@
       <c r="D519" t="n">
         <v>83</v>
       </c>
+      <c r="E519" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="F519" t="n">
+        <v>53.77</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -10817,6 +13935,12 @@
       <c r="D520" t="n">
         <v>81</v>
       </c>
+      <c r="E520" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F520" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -10837,6 +13961,12 @@
       <c r="D521" t="n">
         <v>120</v>
       </c>
+      <c r="E521" t="n">
+        <v>117.56</v>
+      </c>
+      <c r="F521" t="n">
+        <v>93.98</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -10857,6 +13987,12 @@
       <c r="D522" t="n">
         <v>92</v>
       </c>
+      <c r="E522" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="F522" t="n">
+        <v>69.39</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -10877,6 +14013,12 @@
       <c r="D523" t="n">
         <v>84</v>
       </c>
+      <c r="E523" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="F523" t="n">
+        <v>49.48</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -10897,6 +14039,12 @@
       <c r="D524" t="n">
         <v>97</v>
       </c>
+      <c r="E524" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="F524" t="n">
+        <v>77.72</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -10917,6 +14065,12 @@
       <c r="D525" t="n">
         <v>103</v>
       </c>
+      <c r="E525" t="n">
+        <v>123.47</v>
+      </c>
+      <c r="F525" t="n">
+        <v>31.35</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -10937,6 +14091,12 @@
       <c r="D526" t="n">
         <v>71</v>
       </c>
+      <c r="E526" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="F526" t="n">
+        <v>16.61</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -10957,6 +14117,12 @@
       <c r="D527" t="n">
         <v>101</v>
       </c>
+      <c r="E527" t="n">
+        <v>154.72</v>
+      </c>
+      <c r="F527" t="n">
+        <v>35.58</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -10977,6 +14143,12 @@
       <c r="D528" t="n">
         <v>92</v>
       </c>
+      <c r="E528" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="F528" t="n">
+        <v>17.74</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -10997,6 +14169,12 @@
       <c r="D529" t="n">
         <v>91</v>
       </c>
+      <c r="E529" t="n">
+        <v>115.07</v>
+      </c>
+      <c r="F529" t="n">
+        <v>49.9</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -11017,6 +14195,12 @@
       <c r="D530" t="n">
         <v>120</v>
       </c>
+      <c r="E530" t="n">
+        <v>156.7</v>
+      </c>
+      <c r="F530" t="n">
+        <v>102.29</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -11037,6 +14221,12 @@
       <c r="D531" t="n">
         <v>94</v>
       </c>
+      <c r="E531" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="F531" t="n">
+        <v>16.87</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -11057,6 +14247,12 @@
       <c r="D532" t="n">
         <v>127</v>
       </c>
+      <c r="E532" t="n">
+        <v>169.02</v>
+      </c>
+      <c r="F532" t="n">
+        <v>30.68</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -11077,6 +14273,12 @@
       <c r="D533" t="n">
         <v>130</v>
       </c>
+      <c r="E533" t="n">
+        <v>122.52</v>
+      </c>
+      <c r="F533" t="n">
+        <v>63.59</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -11097,6 +14299,12 @@
       <c r="D534" t="n">
         <v>91</v>
       </c>
+      <c r="E534" t="n">
+        <v>142.77</v>
+      </c>
+      <c r="F534" t="n">
+        <v>77.39</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -11117,6 +14325,12 @@
       <c r="D535" t="n">
         <v>127</v>
       </c>
+      <c r="E535" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="F535" t="n">
+        <v>49.16</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -11137,6 +14351,12 @@
       <c r="D536" t="n">
         <v>127</v>
       </c>
+      <c r="E536" t="n">
+        <v>143.73</v>
+      </c>
+      <c r="F536" t="n">
+        <v>67.36</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -11157,6 +14377,12 @@
       <c r="D537" t="n">
         <v>91</v>
       </c>
+      <c r="E537" t="n">
+        <v>79.01000000000001</v>
+      </c>
+      <c r="F537" t="n">
+        <v>16.49</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -11177,6 +14403,12 @@
       <c r="D538" t="n">
         <v>118</v>
       </c>
+      <c r="E538" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="F538" t="n">
+        <v>30.83</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -11197,6 +14429,12 @@
       <c r="D539" t="n">
         <v>121</v>
       </c>
+      <c r="E539" t="n">
+        <v>145.41</v>
+      </c>
+      <c r="F539" t="n">
+        <v>107.69</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -11217,6 +14455,12 @@
       <c r="D540" t="n">
         <v>111</v>
       </c>
+      <c r="E540" t="n">
+        <v>141.67</v>
+      </c>
+      <c r="F540" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -11237,6 +14481,12 @@
       <c r="D541" t="n">
         <v>75</v>
       </c>
+      <c r="E541" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="F541" t="n">
+        <v>11.53</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -11257,6 +14507,12 @@
       <c r="D542" t="n">
         <v>84</v>
       </c>
+      <c r="E542" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="F542" t="n">
+        <v>72.56</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -11277,6 +14533,12 @@
       <c r="D543" t="n">
         <v>123</v>
       </c>
+      <c r="E543" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="F543" t="n">
+        <v>77.41</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -11297,6 +14559,12 @@
       <c r="D544" t="n">
         <v>112</v>
       </c>
+      <c r="E544" t="n">
+        <v>170.07</v>
+      </c>
+      <c r="F544" t="n">
+        <v>89.70999999999999</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -11317,6 +14585,12 @@
       <c r="D545" t="n">
         <v>129</v>
       </c>
+      <c r="E545" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="F545" t="n">
+        <v>63.35</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -11337,6 +14611,12 @@
       <c r="D546" t="n">
         <v>106</v>
       </c>
+      <c r="E546" t="n">
+        <v>100.97</v>
+      </c>
+      <c r="F546" t="n">
+        <v>56.89</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -11357,6 +14637,12 @@
       <c r="D547" t="n">
         <v>102</v>
       </c>
+      <c r="E547" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="F547" t="n">
+        <v>52.7</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -11377,6 +14663,12 @@
       <c r="D548" t="n">
         <v>77</v>
       </c>
+      <c r="E548" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="F548" t="n">
+        <v>50.06</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -11397,6 +14689,12 @@
       <c r="D549" t="n">
         <v>122</v>
       </c>
+      <c r="E549" t="n">
+        <v>152.73</v>
+      </c>
+      <c r="F549" t="n">
+        <v>31.08</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -11417,6 +14715,12 @@
       <c r="D550" t="n">
         <v>129</v>
       </c>
+      <c r="E550" t="n">
+        <v>109.98</v>
+      </c>
+      <c r="F550" t="n">
+        <v>22.25</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -11437,6 +14741,12 @@
       <c r="D551" t="n">
         <v>113</v>
       </c>
+      <c r="E551" t="n">
+        <v>160.51</v>
+      </c>
+      <c r="F551" t="n">
+        <v>43.05</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -11457,6 +14767,12 @@
       <c r="D552" t="n">
         <v>113</v>
       </c>
+      <c r="E552" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="F552" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -11477,6 +14793,12 @@
       <c r="D553" t="n">
         <v>74</v>
       </c>
+      <c r="E553" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="F553" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -11497,6 +14819,12 @@
       <c r="D554" t="n">
         <v>108</v>
       </c>
+      <c r="E554" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="F554" t="n">
+        <v>70.75</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -11517,6 +14845,12 @@
       <c r="D555" t="n">
         <v>73</v>
       </c>
+      <c r="E555" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="F555" t="n">
+        <v>64.05</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -11537,6 +14871,12 @@
       <c r="D556" t="n">
         <v>75</v>
       </c>
+      <c r="E556" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="F556" t="n">
+        <v>16.53</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -11557,6 +14897,12 @@
       <c r="D557" t="n">
         <v>114</v>
       </c>
+      <c r="E557" t="n">
+        <v>105.36</v>
+      </c>
+      <c r="F557" t="n">
+        <v>74.61</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -11577,6 +14923,12 @@
       <c r="D558" t="n">
         <v>101</v>
       </c>
+      <c r="E558" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F558" t="n">
+        <v>48.76</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -11597,6 +14949,12 @@
       <c r="D559" t="n">
         <v>121</v>
       </c>
+      <c r="E559" t="n">
+        <v>180.22</v>
+      </c>
+      <c r="F559" t="n">
+        <v>96.93000000000001</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -11617,6 +14975,12 @@
       <c r="D560" t="n">
         <v>99</v>
       </c>
+      <c r="E560" t="n">
+        <v>154.13</v>
+      </c>
+      <c r="F560" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -11637,6 +15001,12 @@
       <c r="D561" t="n">
         <v>116</v>
       </c>
+      <c r="E561" t="n">
+        <v>127.44</v>
+      </c>
+      <c r="F561" t="n">
+        <v>77.66</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -11657,6 +15027,12 @@
       <c r="D562" t="n">
         <v>104</v>
       </c>
+      <c r="E562" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="F562" t="n">
+        <v>80.97</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -11677,6 +15053,12 @@
       <c r="D563" t="n">
         <v>124</v>
       </c>
+      <c r="E563" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="F563" t="n">
+        <v>106.45</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -11697,6 +15079,12 @@
       <c r="D564" t="n">
         <v>109</v>
       </c>
+      <c r="E564" t="n">
+        <v>122.84</v>
+      </c>
+      <c r="F564" t="n">
+        <v>72.20999999999999</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -11717,6 +15105,12 @@
       <c r="D565" t="n">
         <v>121</v>
       </c>
+      <c r="E565" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F565" t="n">
+        <v>63.27</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -11737,6 +15131,12 @@
       <c r="D566" t="n">
         <v>85</v>
       </c>
+      <c r="E566" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="F566" t="n">
+        <v>52.14</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -11757,6 +15157,12 @@
       <c r="D567" t="n">
         <v>82</v>
       </c>
+      <c r="E567" t="n">
+        <v>112.57</v>
+      </c>
+      <c r="F567" t="n">
+        <v>65.73999999999999</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -11777,6 +15183,12 @@
       <c r="D568" t="n">
         <v>119</v>
       </c>
+      <c r="E568" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="F568" t="n">
+        <v>68.78</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -11797,6 +15209,12 @@
       <c r="D569" t="n">
         <v>129</v>
       </c>
+      <c r="E569" t="n">
+        <v>106</v>
+      </c>
+      <c r="F569" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -11817,6 +15235,12 @@
       <c r="D570" t="n">
         <v>111</v>
       </c>
+      <c r="E570" t="n">
+        <v>108.51</v>
+      </c>
+      <c r="F570" t="n">
+        <v>94.15000000000001</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -11837,6 +15261,12 @@
       <c r="D571" t="n">
         <v>99</v>
       </c>
+      <c r="E571" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F571" t="n">
+        <v>66.05</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -11857,6 +15287,12 @@
       <c r="D572" t="n">
         <v>88</v>
       </c>
+      <c r="E572" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="F572" t="n">
+        <v>57.85</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -11877,6 +15313,12 @@
       <c r="D573" t="n">
         <v>86</v>
       </c>
+      <c r="E573" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="F573" t="n">
+        <v>26.81</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -11897,6 +15339,12 @@
       <c r="D574" t="n">
         <v>125</v>
       </c>
+      <c r="E574" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="F574" t="n">
+        <v>80.52</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -11917,6 +15365,12 @@
       <c r="D575" t="n">
         <v>88</v>
       </c>
+      <c r="E575" t="n">
+        <v>126.71</v>
+      </c>
+      <c r="F575" t="n">
+        <v>39.2</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -11937,6 +15391,12 @@
       <c r="D576" t="n">
         <v>97</v>
       </c>
+      <c r="E576" t="n">
+        <v>91.45999999999999</v>
+      </c>
+      <c r="F576" t="n">
+        <v>61.93</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -11956,6 +15416,12 @@
       </c>
       <c r="D577" t="n">
         <v>127</v>
+      </c>
+      <c r="E577" t="n">
+        <v>167.92</v>
+      </c>
+      <c r="F577" t="n">
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
